--- a/docs/PTC_Mask_Transfer_4Axis_Design_Draft.xlsx
+++ b/docs/PTC_Mask_Transfer_4Axis_Design_Draft.xlsx
@@ -33,6 +33,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_Barcode_History設計" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_HMI_4軸畫面" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_4軸CODEX封口清單" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_IO不可新增與待確認" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -2715,15 +2716,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="72" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2735,32 +2736,27 @@
       </c>
       <c r="B1" s="14" t="inlineStr">
         <is>
-          <t>名稱</t>
+          <t>動作</t>
         </is>
       </c>
       <c r="C1" s="14" t="inlineStr">
         <is>
-          <t>進入條件</t>
+          <t>執行輸出/命令</t>
         </is>
       </c>
       <c r="D1" s="14" t="inlineStr">
         <is>
-          <t>主要動作</t>
+          <t>完成條件</t>
         </is>
       </c>
       <c r="E1" s="14" t="inlineStr">
         <is>
-          <t>完成條件</t>
+          <t>異常/Timeout</t>
         </is>
       </c>
       <c r="F1" s="14" t="inlineStr">
         <is>
-          <t>異常/Timeout</t>
-        </is>
-      </c>
-      <c r="G1" s="14" t="inlineStr">
-        <is>
-          <t>M/D/IO</t>
+          <t>備註</t>
         </is>
       </c>
     </row>
@@ -2772,32 +2768,27 @@
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>Z/Barcode入口</t>
+          <t>Z/Barcode流程入口</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>M6101 ON + M6100 ON + X0000安全OK + X0001氣壓OK</t>
+          <t>SET M6102；RST M6103</t>
         </is>
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>SET M6102；RST M6103；確認X已離開檢查位干涉區。</t>
+          <t>X0000安全OK、X0001氣壓OK、X0036 FFU Run、X0037 OFF</t>
         </is>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
-          <t>進S301</t>
+          <t>NG-&gt;S389</t>
         </is>
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>K171</t>
-        </is>
-      </c>
-      <c r="G2" s="16" t="inlineStr">
-        <is>
-          <t>M6100/M6101/M6102</t>
+          <t>Auto只允許Axis1/2/3；Axis4不參與</t>
         </is>
       </c>
     </row>
@@ -2809,32 +2800,27 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>左右定位伸出</t>
+          <t>檢查站左右定位伸出</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>S300</t>
+          <t>Y0011 ON、Y0012 OFF</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>Y0025 ON，左右定位氣缸伸出。</t>
+          <t>X0016 ON</t>
         </is>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
-          <t>X0044 ON</t>
+          <t>Timeout K310</t>
         </is>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>K180</t>
-        </is>
-      </c>
-      <c r="G3" s="16" t="inlineStr">
-        <is>
-          <t>LR Extend Complete</t>
+          <t>使用既有正式點位，不新增Y0025/X0044</t>
         </is>
       </c>
     </row>
@@ -2846,32 +2832,27 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>前後定位伸出</t>
+          <t>檢查站前後定位伸出</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>X0044 ON</t>
+          <t>Y0013 ON、Y0014 OFF</t>
         </is>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>Y0026 ON，前後定位氣缸伸出。</t>
+          <t>X0020 ON</t>
         </is>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
-          <t>X0046 ON</t>
+          <t>Timeout K311</t>
         </is>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>K180</t>
-        </is>
-      </c>
-      <c r="G4" s="16" t="inlineStr">
-        <is>
-          <t>FB Extend Complete</t>
+          <t>使用既有正式點位，不新增Y0026/X0046</t>
         </is>
       </c>
     </row>
@@ -2883,32 +2864,27 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>光罩在席確認</t>
+          <t>確認光罩在檢查站</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>X0044 ON + X0046 ON</t>
+          <t>無</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>確認檢查站光罩在席。</t>
+          <t>X0026 ON</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
-          <t>X0026 ON</t>
+          <t>K312 光罩不在席</t>
         </is>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
-          <t>K230</t>
-        </is>
-      </c>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>Inspection Mask Present</t>
+          <t>Z升起前必要條件</t>
         </is>
       </c>
     </row>
@@ -2920,32 +2896,27 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>Z升到Platform位</t>
+          <t>Z升降到平台位，將光罩抬高</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>X0026 ON</t>
+          <t>SET M4521；目標D4514</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>SET M4521，Axis3到D4514。</t>
+          <t>M4551 ON + Busy OFF + 誤差&lt;=D4504</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>M4551 ON</t>
+          <t>K320</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>K240</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>D4514/M4551</t>
+          <t>平台位高度現場實測</t>
         </is>
       </c>
     </row>
@@ -2957,32 +2928,27 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>定位氣缸縮回</t>
+          <t>檢查站左右/前後定位縮回</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>M4551 ON</t>
+          <t>Y0011 OFF、Y0012 ON、Y0013 OFF、Y0014 ON</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>Y0025 OFF、Y0026 OFF。</t>
+          <t>X0017 ON 且 X0021 ON</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>X0045 ON + X0047 ON</t>
+          <t>K321</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
-          <t>K180</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>LR/FB Retract Complete</t>
+          <t>定位縮回後才可進Barcode高度</t>
         </is>
       </c>
     </row>
@@ -2994,32 +2960,27 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>Z到Barcode掃描位</t>
+          <t>Z升降到Barcode掃描位</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>X0045/X0047 ON</t>
+          <t>SET M4522；目標D4510</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>SET M4522，Axis3到D4510。</t>
+          <t>M4552 ON + Busy OFF + 誤差&lt;=D4504</t>
         </is>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>M4552 ON</t>
+          <t>K322</t>
         </is>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>K240</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>D4510/M4552</t>
+          <t>Barcode高度現場實測</t>
         </is>
       </c>
     </row>
@@ -3036,27 +2997,22 @@
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>M4552 ON</t>
+          <t>M6300 ON時SET M6302；M6300 OFF則SET M6306</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>若M6300 ON，SET M6302觸發SR-2000W；若OFF，SET M6306 Bypass。</t>
+          <t>M6303 ON 或 M6306 ON</t>
         </is>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>M6303 ON或M6306 ON</t>
+          <t>K330</t>
         </is>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>K181</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>D6300/D6350/D6400/D6422</t>
+          <t>KEYENCE SR-2000W；通訊格式需實測</t>
         </is>
       </c>
     </row>
@@ -3073,27 +3029,22 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>M6303 ON</t>
+          <t>PLC/HMI比對D6300~D6349與D6350~D6399</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>Mask Barcode與Storage Barcode比對。</t>
+          <t>M6304 OK-&gt;S309；M6305 NG-&gt;S380</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>M6304 OK進S309；M6305 NG進S380</t>
+          <t>K331</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>K182</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>D6402/D6412</t>
+          <t>Barcode OFF 記錄BYPASS</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3056,27 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>Visual人工確認</t>
+          <t>人工目視檢查選配</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>M6304 ON</t>
+          <t>M6500 ON時SET M6501；OFF則SET M6504</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>若M6500 ON，SET M6501 HMI彈窗Hold；若OFF，SET M6504 Bypass。</t>
+          <t>M6502 OK/M6504-&gt;S310；M6503 NG-&gt;S380</t>
         </is>
       </c>
       <c r="E11" s="16" t="inlineStr">
         <is>
-          <t>M6502 OK或M6504 ON；M6503 NG進S380</t>
+          <t>K340</t>
         </is>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>K260</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>D6500/D6502</t>
+          <t>HMI彈窗，不需要操作紀錄</t>
         </is>
       </c>
     </row>
@@ -3142,133 +3088,117 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>Z回Home/安全等待位</t>
+          <t>Z升降回安全/原點等待位</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>Barcode/Visual OK</t>
+          <t>SET M4520；目標D4512</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>SET M4520，Axis3回D4512。</t>
+          <t>M4550或M4553 ON + Busy OFF</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
-          <t>M4550或M4553 ON</t>
+          <t>K350</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>K240</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>Z Safe For X</t>
+          <t>完成後通知X回檢查位</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>S311</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>通知X可回檢查位</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>Z安全位完成</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>SET M6103；RST M6102。</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>RETSTL</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr"/>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>X流程接續S131/S163</t>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Z/Barcode完成交握</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>SET M6103；RST M6102</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>主流程收到M6103</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr"/>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>M6103=Z/Barcode流程完成且Z升降在安全位</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>S380</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>NG Return判定</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>Barcode NG或Visual NG</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>依方向決定Return：正向回Storage、反向回Load。</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>交給X流程Return sequence</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>K182/K260</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>不得直接PASS。</t>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>NG返回來源盒</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>依方向回儲存盒或上機盒</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>X軸完成回放</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>必要時HMI確認</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>不得自動轉Axis4</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>S389</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>Z/Barcode異常</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>任一停機異常</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>RST M6102；不SET M6103；寫D6004/D6006/D6008。</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>HMI復歸後回初始化</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr"/>
-      <c r="G15" s="18" t="inlineStr"/>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Z/Barcode異常監控</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>SET Alarm Code；RST M6102</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>HMI排除後回初始化/安全位</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr"/>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>停機或警告依Alarm表</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7820,13 +7750,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
     <col width="54" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
@@ -7834,384 +7764,242 @@
     <row r="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>項目</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="B1" s="14" t="inlineStr">
         <is>
-          <t>軸/功能</t>
+          <t>設計結論</t>
         </is>
       </c>
       <c r="C1" s="14" t="inlineStr">
         <is>
-          <t>狀態</t>
+          <t>正式依據</t>
         </is>
       </c>
       <c r="D1" s="14" t="inlineStr">
         <is>
-          <t>設計結論</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>資料來源/銜接</t>
-        </is>
-      </c>
-      <c r="F1" s="14" t="inlineStr">
-        <is>
-          <t>Coding前注意</t>
+          <t>備註</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>設計版本</t>
-        </is>
-      </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>4軸完整需求</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>PASS_TO_CODING_DRAFT</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="inlineStr">
-        <is>
-          <t>由既有PLC/HMI標準版複製為新手稿，並整合20260825 4軸完整需求建議表。</t>
-        </is>
-      </c>
-      <c r="E2" s="17" t="inlineStr">
-        <is>
-          <t>舊標準版全部保留；本表新增/修正4軸設計。</t>
-        </is>
-      </c>
-      <c r="F2" s="17" t="inlineStr">
-        <is>
-          <t>這是新設計手稿，不是現場Release。</t>
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>設計原則</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>正式X/Y點位只依BOM/PLC點位表，不再新增臨時X/Y</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>02_XY點位表</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>新需求若無正式點位，放到26_IO不可新增與待確認</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>Axis1</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>X橫移</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t>Auto + Manual/Teach。自動負責Storage/Inspection/Load三位置移動。</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>沿用M4100~M4299、D4100~D4299、S100/S150/S190。</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>S119/S161不得提早SET M6100。</t>
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Axis1 X橫移</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>使用既有X0002/X0003/X0004與Y0003</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>04_M軸1、10_S100/S150</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>左位/檢查位/右位/原點</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>Axis2</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>X升降</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t>Auto + Manual/Teach。負責取/放/真空確認/上位。</t>
-        </is>
-      </c>
-      <c r="E4" s="17" t="inlineStr">
-        <is>
-          <t>沿用M4300~M4499、D4300~D4499、S200~S299。</t>
-        </is>
-      </c>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t>M4330只作真空確認位命令；JOG用M4340/M4341。</t>
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Axis2 X升降</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>使用既有X0005/X0006/X0007與Y0001/Y0004</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>05_M軸2、11_S200</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>取位/放位/真空確認位/上位</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>Axis3</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>Z升降</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>可Coding</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>Auto + Manual/Teach。自動負責Platform、Barcode Scan、Home/Safe位。</t>
-        </is>
-      </c>
-      <c r="E5" s="19" t="inlineStr">
-        <is>
-          <t>新增M4500~M4699、D4500~D4699、S300~S399。</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>Z高度與Tolerance需實測。</t>
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>X軸夾爪/真空</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>使用既有X0014/X0015/X0027與Y0007/Y0010/Y0015/Y0016</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>02_XY點位表</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>取片：夾爪關-&gt;真空ON-&gt;真空OK-&gt;上升10mm-&gt;再確認真空OK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Axis4</t>
+          <t>檢查站定位</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>Z旋轉</t>
+          <t>使用既有X0016/X0017/X0020/X0021與Y0011~Y0014</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>手動限定</t>
+          <t>02_XY點位表</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>Manual/Teach only。Auto禁止使用Axis4旋轉命令。</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>新增/整理M4700~M4899、D4700~D4899、S400~S499。</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>0/90/180/270只給工程調機；回原點後必須移到0位。</t>
+          <t>不得新增X0044~X0047/Y0025~Y0026</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>Auto軸數</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Axis1+Axis2+Axis3</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>自動流程只使用3軸；Axis4在Auto中鎖住。</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>M6010/M6400才允許Axis4手動。</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>程式內不得由Barcode OK觸發Axis4。</t>
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>儲存盒/上機盒</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>使用既有X0022~X0025、X0030/X0031、Y0017/Y0020/Y0021/Y0022</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>02_XY點位表</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>盒存在與破真空都有既有點位</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>Z檢查站定位</t>
+          <t>Axis3 Z升降</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>左右+前後定位</t>
+          <t>Auto可用，配合Barcode與檢查站定位</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>12_S300</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>四支定位氣缸回授合併為4個DI，兩組DO控制。</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>X0044~X0047、Y0025~Y0026。</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>兩支同組氣缸需全部到位才算完成。</t>
+          <t>D4510 Barcode高度、D4514平台位、D4504容許誤差</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>Barcode</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>SR-2000W</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>可Coding</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>Barcode Enable=ON時，Storage Barcode必須Valid才允許Auto Start；Mask Barcode比對NG走Return。</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>D6300/D6350/D6400/D642x。</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>1000筆History建議用HMI Ring Buffer/Data Logging。</t>
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Axis4 Z旋轉</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>只允許工程/手動調機，不進Auto</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>13_S400</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>0/90/180/270測試；Auto不得命令Axis4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>Visual</t>
+          <t>HMI</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>人工目視確認</t>
+          <t>要有Auto、4軸手動調機、Barcode、Visual、Alarm、I/O監看</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>14/24_HMI</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>Visual Enable=ON時，Barcode OK後HMI彈窗Hold，人工OK才繼續；NG走Return。</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>M6500~M6515、D6500~D6519。</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>Visual OFF時Bypass，但需HMI顯示。</t>
+          <t>手動調機須受安全/工程模式限制</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>Cycle Complete</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>完成取盒流程</t>
+          <t>可進PLC/HMI Coding；現場Release仍HOLD</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>16_驗收</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>流程完成後HMI提示允許開門、盒蓋關閉後破真空，取出兩盒後Cycle Complete。</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>X0022/X0024與新增盒蓋DI、Y0030/Y0031。</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>安全門Unlock只送請求，硬體安全仍由安全迴路決定。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>Release Gate</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>整機</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>文件可進PLC/HMI Coding；現場Release仍需實測。</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>保留16_驗收_Release_Gate。</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>SR-2000W、Visual操作、Z定位、真空/安全策略需實機封口。</t>
+          <t>SR-2000W、Z高度、Tolerance、Safety Stop需實測</t>
         </is>
       </c>
     </row>
@@ -10417,15 +10205,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
@@ -10455,3816 +10243,1964 @@
       </c>
       <c r="E1" s="14" t="inlineStr">
         <is>
-          <t>Active Level</t>
+          <t>來源/判定</t>
         </is>
       </c>
       <c r="F1" s="14" t="inlineStr">
         <is>
-          <t>NPN/PNP/接點</t>
-        </is>
-      </c>
-      <c r="G1" s="14" t="inlineStr">
-        <is>
-          <t>COM</t>
-        </is>
-      </c>
-      <c r="H1" s="14" t="inlineStr">
-        <is>
-          <t>Terminal</t>
-        </is>
-      </c>
-      <c r="I1" s="14" t="inlineStr">
-        <is>
-          <t>Cable/Drawing Ref</t>
-        </is>
-      </c>
-      <c r="J1" s="14" t="inlineStr">
-        <is>
-          <t>設計說明</t>
+          <t>設計備註</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>X0000</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>安全繼電器OK</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
-        <is>
-          <t>ON=安全成立</t>
-        </is>
-      </c>
-      <c r="E2" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F2" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G2" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM0</t>
-        </is>
-      </c>
-      <c r="H2" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0000</t>
-        </is>
-      </c>
-      <c r="I2" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J2" s="16" t="inlineStr">
-        <is>
-          <t>安全迴路總回授，PLC只監看。</t>
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>ON=安全迴路OK</t>
+        </is>
+      </c>
+      <c r="E2" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F2" s="17" t="inlineStr">
+        <is>
+          <t>安全回授；Auto/Manual共同條件</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>X0001</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>氣壓源OK</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>ON=氣壓正常</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F3" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G3" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM0</t>
-        </is>
-      </c>
-      <c r="H3" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0001</t>
-        </is>
-      </c>
-      <c r="I3" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J3" s="16" t="inlineStr">
-        <is>
-          <t>氣壓不足停機。</t>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>低氣壓停機條件</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>X0002</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>X軸橫移_負極限</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>ON=極限觸發</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G4" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM0</t>
-        </is>
-      </c>
-      <c r="H4" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0002</t>
-        </is>
-      </c>
-      <c r="I4" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J4" s="16" t="inlineStr">
-        <is>
-          <t>軸卡RLS/PLC監看。</t>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>Axis1 RLS</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>X0003</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>X軸橫移_原點</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>ON=原點</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM0</t>
-        </is>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0003</t>
-        </is>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J5" s="16" t="inlineStr">
-        <is>
-          <t>DOG/原點。</t>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>Axis1 DOG</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>X0004</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>X軸橫移_正極限</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>ON=極限觸發</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM0</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0004</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>軸卡FLS/PLC監看。</t>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>Axis1 FLS</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>X0005</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>X軸升降_負極限</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>ON=極限觸發</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM0</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0005</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>軸卡RLS/PLC監看。</t>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>Axis2 RLS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>X0006</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>X軸升降_原點</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>ON=原點</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM0</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0006</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>DOG/原點。</t>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>Axis2 DOG</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>X0007</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>X軸升降_正極限</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>ON=極限觸發</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM0</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0007</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>軸卡FLS/PLC監看。</t>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>Axis2 FLS</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>X0010</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Z軸升降_負極限</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>ON=極限觸發</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM0</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0010</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>Z升降限位。</t>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>Axis3 RLS</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>X0011</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Z軸升降_原點</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>ON=原點</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM0</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0011</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>Z升降原點。</t>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>Axis3 DOG</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>X0012</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Z軸升降_正極限</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>ON=極限觸發</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM0</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0012</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>Z升降限位。</t>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>Axis3 FLS</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>X0013</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Z軸旋轉_原點</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>ON=原點</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM0</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0013</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>Z旋轉原點。</t>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>Axis4 DOG；手動/調機用</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>X0014</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>X軸氣缸左右夾爪_開</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>ON=開到位</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM1</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0014</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>夾爪開確認。</t>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>ON=開完成</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>取放片夾爪開確認</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>X0015</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>X軸氣缸左右夾爪_關</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>ON=關到位</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM1</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0015</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>夾爪關確認。</t>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>ON=關完成</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>取片夾爪閉合確認</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>X0016</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>檢查站氣缸左右定位_開</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>ON=開到位</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM1</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0016</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>檢查站定位。</t>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>ON=開完成</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>Z/Barcode流程使用；使用本列正式點位</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>X0017</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>檢查站氣缸左右定位_關</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>ON=關到位</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM1</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0017</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>檢查站定位。</t>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>ON=關完成</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>Z/Barcode流程使用；使用本列正式點位</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>X0020</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>檢查站氣缸前後定位_開</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>ON=開到位</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM1</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0020</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>檢查站定位。</t>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>ON=開完成</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>Z/Barcode流程使用；使用本列正式點位</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>X0021</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>檢查站氣缸前後定位_關</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>ON=關到位</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM1</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0021</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>檢查站定位。</t>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>ON=關完成</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>Z/Barcode流程使用；使用本列正式點位</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>X0022</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>儲存盒在席定位</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>ON=盒在席</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM1</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0022</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>盒在席，不等於盒內光罩存在。</t>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>ON=在席</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>盒子在席；流程完成後兩盒移除判斷之一</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>X0023</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>儲存盒開蓋定位</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>ON=開蓋到位</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM1</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0023</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>儲存盒開蓋。</t>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>ON=開蓋定位完成</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>依機構定義使用</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>X0024</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>上機盒在席定位</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>ON=盒在席</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM1</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0024</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>盒在席，不等於盒內光罩存在。</t>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>ON=在席</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>盒子在席；流程完成後兩盒移除判斷之一</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>X0025</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>上機盒開蓋定位</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>ON=開蓋到位</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM1</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0025</t>
-        </is>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>上機盒開蓋。</t>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>ON=開蓋定位完成</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>依機構定義使用</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>X0026</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>光罩在席定位</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>ON=檢查站有光罩</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM1</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0026</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>檢查站光罩存在實體輸入。</t>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>Z升降前必須確認</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>X0027</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>X軸手臂真空OK</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>ON=吸附成立</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM1</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0027</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>手臂吸附確認。</t>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>ON=真空建立</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>X升降取片與移動前確認</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>X0030</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>儲存盒真空OK</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>ON=真空成立</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM1</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0030</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>儲存盒光罩存在由真空OK+流程狀態推導。</t>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>ON=真空建立</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>儲存盒吸附狀態</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>X0031</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>上機盒真空OK</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>ON=真空成立</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM1</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0031</t>
-        </is>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>上機盒光罩存在由真空OK+流程狀態推導。</t>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>ON=真空建立</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>上機盒吸附狀態</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>X0032</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>靜電消除器檢查</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>ON=Check</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM2</t>
-        </is>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0032</t>
-        </is>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>警告。</t>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>警告/維護提示，不一定停機</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>X0033</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>靜電消除器異常</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>ON=Alarm</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM2</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0033</t>
-        </is>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>停機。</t>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>依Enable設定決定警告或停機</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>X0034</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>排風壓差低</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>ON=Low</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>乾接點/24V回路</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM2</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0034</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>Dwyer壓差表警報回授。</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="n"/>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>警告或停機由參數決定</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>X0035</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>排風壓差高</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>ON=High</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>乾接點/24V回路</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM2</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0035</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>Dwyer壓差表警報回授。</t>
-        </is>
-      </c>
-      <c r="J31" s="16" t="n"/>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>警告或停機由參數決定</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>X0036</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>FFU運轉中</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>ON=Run</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM2</t>
-        </is>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0036</t>
-        </is>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>若FFU有Run接點才接。</t>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>Auto Ready必要條件</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>X0037</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>FFU異常</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>ON=Alarm</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>DI-COM2</t>
-        </is>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0037</t>
-        </is>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
-        <is>
-          <t>若FFU有Alarm接點才接。</t>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>Auto禁止/停機條件</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>X0040</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>EMO1</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>ON=EMO正常/輔助接點</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>擴充DI-COM</t>
-        </is>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0040</t>
-        </is>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>PLC監看用，不取代安全迴路。</t>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>ON=EMO正常/未按下</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>PLC監看；安全切斷仍走安全繼電器硬體</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>X0041</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>EMO2</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C35" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>ON=EMO正常/輔助接點</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>擴充DI-COM</t>
-        </is>
-      </c>
-      <c r="H35" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0041</t>
-        </is>
-      </c>
-      <c r="I35" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J35" s="16" t="inlineStr">
-        <is>
-          <t>PLC監看用。</t>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>ON=EMO正常/未按下</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>PLC監看</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>X0042</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>EMO3</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>ON=EMO正常/輔助接點</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F36" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G36" s="16" t="inlineStr">
-        <is>
-          <t>擴充DI-COM</t>
-        </is>
-      </c>
-      <c r="H36" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0042</t>
-        </is>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J36" s="16" t="inlineStr">
-        <is>
-          <t>PLC監看用。</t>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>ON=EMO正常/未按下</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>PLC監看</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>X0043</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>EMO4</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
-        <is>
-          <t>ON=EMO正常/輔助接點</t>
-        </is>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G37" s="16" t="inlineStr">
-        <is>
-          <t>擴充DI-COM</t>
-        </is>
-      </c>
-      <c r="H37" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0043</t>
-        </is>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J37" s="16" t="inlineStr">
-        <is>
-          <t>PLC監看用。</t>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>ON=EMO正常/未按下</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>PLC監看</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>Y0000</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>安全繼電器復歸</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>安全繼電器復歸(Relay)</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>瞬時ON</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM0</t>
-        </is>
-      </c>
-      <c r="H38" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0000</t>
-        </is>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J38" s="16" t="inlineStr">
-        <is>
-          <t>Safety Reset Request後瞬時輸出。</t>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>瞬間ON</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>HMI Reset觸發PLC輸出復歸</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>Y0001</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>X軸升降煞車</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>X軸升降煞車(Relay)</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>ON=釋放煞車</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出+Relay建議</t>
-        </is>
-      </c>
-      <c r="G39" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM0</t>
-        </is>
-      </c>
-      <c r="H39" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0001</t>
-        </is>
-      </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J39" s="16" t="inlineStr">
-        <is>
-          <t>Z/垂直軸需與伺服Ready互鎖。</t>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>ON=煞車釋放</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t>有煞車軸使用Relay控制</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>Y0002</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>Z軸升降煞車</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>Z軸升降煞車(Relay)</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>ON=釋放煞車</t>
-        </is>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出+Relay建議</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM0</t>
-        </is>
-      </c>
-      <c r="H40" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0002</t>
-        </is>
-      </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>Z升降垂直軸。</t>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>ON=煞車釋放</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>有煞車軸使用Relay控制</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>Y0003</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>X軸橫移伺服電源</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>X軸橫移伺服電源(Relay)</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D41" s="17" t="inlineStr">
         <is>
           <t>ON=MC吸合</t>
         </is>
       </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F41" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出+Relay/接觸器</t>
-        </is>
-      </c>
-      <c r="G41" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM0</t>
-        </is>
-      </c>
-      <c r="H41" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0003</t>
-        </is>
-      </c>
-      <c r="I41" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J41" s="16" t="inlineStr">
-        <is>
-          <t>伺服電源接觸器。</t>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>Axis1 Servo main power</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>Y0004</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>X軸升降伺服電源</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>X軸升降伺服電源(Relay)</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="D42" s="17" t="inlineStr">
         <is>
           <t>ON=MC吸合</t>
         </is>
       </c>
-      <c r="E42" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出+Relay/接觸器</t>
-        </is>
-      </c>
-      <c r="G42" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM0</t>
-        </is>
-      </c>
-      <c r="H42" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0004</t>
-        </is>
-      </c>
-      <c r="I42" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J42" s="16" t="inlineStr">
-        <is>
-          <t>伺服電源接觸器。</t>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>Axis2 Servo main power</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>Y0005</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
-        <is>
-          <t>Z軸升降伺服電源</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="inlineStr">
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>Z軸升降伺服電源(Relay)</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D43" s="16" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>ON=MC吸合</t>
         </is>
       </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F43" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出+Relay/接觸器</t>
-        </is>
-      </c>
-      <c r="G43" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM0</t>
-        </is>
-      </c>
-      <c r="H43" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0005</t>
-        </is>
-      </c>
-      <c r="I43" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
-        <is>
-          <t>伺服電源接觸器。</t>
+      <c r="E43" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>Axis3 Servo main power</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="inlineStr">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>Y0006</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>Z軸旋轉伺服電源</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="inlineStr">
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>Z軸旋轉伺服電源(Relay)</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D44" s="17" t="inlineStr">
         <is>
           <t>ON=MC吸合</t>
         </is>
       </c>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出+Relay/接觸器</t>
-        </is>
-      </c>
-      <c r="G44" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM0</t>
-        </is>
-      </c>
-      <c r="H44" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0006</t>
-        </is>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
-        <is>
-          <t>伺服電源接觸器。</t>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>Axis4 Servo main power</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>Y0007</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B45" s="17" t="inlineStr">
         <is>
           <t>X軸左右氣缸電磁閥_開</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
+      <c r="C45" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>ON=開</t>
         </is>
       </c>
-      <c r="E45" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅/需突波吸收</t>
-        </is>
-      </c>
-      <c r="G45" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM1</t>
-        </is>
-      </c>
-      <c r="H45" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0007</t>
-        </is>
-      </c>
-      <c r="I45" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J45" s="16" t="inlineStr">
-        <is>
-          <t>依電磁閥線圈電流確認。</t>
+      <c r="E45" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>夾爪開</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="inlineStr">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>Y0010</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B46" s="17" t="inlineStr">
         <is>
           <t>X軸左右氣缸電磁閥_關</t>
         </is>
       </c>
-      <c r="C46" s="16" t="inlineStr">
+      <c r="C46" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>ON=關</t>
         </is>
       </c>
-      <c r="E46" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅/需突波吸收</t>
-        </is>
-      </c>
-      <c r="G46" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM1</t>
-        </is>
-      </c>
-      <c r="H46" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0010</t>
-        </is>
-      </c>
-      <c r="I46" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J46" s="16" t="inlineStr"/>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>夾爪關</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="inlineStr">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>Y0011</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B47" s="17" t="inlineStr">
         <is>
           <t>檢查站左右電磁閥_開</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="C47" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
-        <is>
-          <t>ON=開</t>
-        </is>
-      </c>
-      <c r="E47" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F47" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅/需突波吸收</t>
-        </is>
-      </c>
-      <c r="G47" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM1</t>
-        </is>
-      </c>
-      <c r="H47" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0011</t>
-        </is>
-      </c>
-      <c r="I47" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J47" s="16" t="inlineStr"/>
+      <c r="D47" s="17" t="inlineStr">
+        <is>
+          <t>ON=定位伸出</t>
+        </is>
+      </c>
+      <c r="E47" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F47" s="17" t="inlineStr">
+        <is>
+          <t>Z/Barcode流程使用；使用本列正式點位</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>Y0012</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>檢查站左右電磁閥_關</t>
         </is>
       </c>
-      <c r="C48" s="16" t="inlineStr">
+      <c r="C48" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D48" s="16" t="inlineStr">
-        <is>
-          <t>ON=關</t>
-        </is>
-      </c>
-      <c r="E48" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅/需突波吸收</t>
-        </is>
-      </c>
-      <c r="G48" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM1</t>
-        </is>
-      </c>
-      <c r="H48" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0012</t>
-        </is>
-      </c>
-      <c r="I48" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J48" s="16" t="inlineStr"/>
+      <c r="D48" s="17" t="inlineStr">
+        <is>
+          <t>ON=定位縮回</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>Z/Barcode流程使用</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="inlineStr">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>Y0013</t>
         </is>
       </c>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>檢查站前後電磁閥_開</t>
         </is>
       </c>
-      <c r="C49" s="16" t="inlineStr">
+      <c r="C49" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D49" s="16" t="inlineStr">
-        <is>
-          <t>ON=開</t>
-        </is>
-      </c>
-      <c r="E49" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅/需突波吸收</t>
-        </is>
-      </c>
-      <c r="G49" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM1</t>
-        </is>
-      </c>
-      <c r="H49" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0013</t>
-        </is>
-      </c>
-      <c r="I49" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J49" s="16" t="inlineStr"/>
+      <c r="D49" s="17" t="inlineStr">
+        <is>
+          <t>ON=定位伸出</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="inlineStr">
+        <is>
+          <t>Z/Barcode流程使用；使用本列正式點位</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>Y0014</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B50" s="17" t="inlineStr">
         <is>
           <t>檢查站前後電磁閥_關</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C50" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>ON=關</t>
-        </is>
-      </c>
-      <c r="E50" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅/需突波吸收</t>
-        </is>
-      </c>
-      <c r="G50" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM1</t>
-        </is>
-      </c>
-      <c r="H50" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0014</t>
-        </is>
-      </c>
-      <c r="I50" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J50" s="16" t="inlineStr"/>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>ON=定位縮回</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>Z/Barcode流程使用</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="inlineStr">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>Y0015</t>
         </is>
       </c>
-      <c r="B51" s="16" t="inlineStr">
-        <is>
-          <t>X軸手臂真空ON</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>X軸手臂真空ON(Relay)</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D51" s="16" t="inlineStr">
+      <c r="D51" s="17" t="inlineStr">
         <is>
           <t>ON=真空</t>
         </is>
       </c>
-      <c r="E51" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F51" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅/需突波吸收</t>
-        </is>
-      </c>
-      <c r="G51" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM1</t>
-        </is>
-      </c>
-      <c r="H51" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0015</t>
-        </is>
-      </c>
-      <c r="I51" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J51" s="16" t="inlineStr">
-        <is>
-          <t>異常時是否保持依Fault Matrix。</t>
+      <c r="E51" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F51" s="17" t="inlineStr">
+        <is>
+          <t>X手臂吸盤真空</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="inlineStr">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>Y0016</t>
         </is>
       </c>
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>X軸手臂破真空</t>
-        </is>
-      </c>
-      <c r="C52" s="16" t="inlineStr">
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>X軸手臂破真空(Relay)</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="D52" s="17" t="inlineStr">
         <is>
           <t>ON=破真空</t>
         </is>
       </c>
-      <c r="E52" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅/需突波吸收</t>
-        </is>
-      </c>
-      <c r="G52" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM1</t>
-        </is>
-      </c>
-      <c r="H52" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0016</t>
-        </is>
-      </c>
-      <c r="I52" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J52" s="16" t="inlineStr"/>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>X手臂放片</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>Y0017</t>
         </is>
       </c>
-      <c r="B53" s="16" t="inlineStr">
-        <is>
-          <t>儲存盒真空ON</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr">
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>儲存盒真空ON(Relay)</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D53" s="16" t="inlineStr">
+      <c r="D53" s="17" t="inlineStr">
         <is>
           <t>ON=真空</t>
         </is>
       </c>
-      <c r="E53" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F53" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅/需突波吸收</t>
-        </is>
-      </c>
-      <c r="G53" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM1</t>
-        </is>
-      </c>
-      <c r="H53" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0017</t>
-        </is>
-      </c>
-      <c r="I53" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J53" s="16" t="inlineStr"/>
+      <c r="E53" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F53" s="17" t="inlineStr">
+        <is>
+          <t>儲存盒吸附</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="inlineStr">
+      <c r="A54" s="17" t="inlineStr">
         <is>
           <t>Y0020</t>
         </is>
       </c>
-      <c r="B54" s="16" t="inlineStr">
-        <is>
-          <t>儲存盒破真空</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="inlineStr">
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>儲存盒破真空(Relay)</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D54" s="16" t="inlineStr">
+      <c r="D54" s="17" t="inlineStr">
         <is>
           <t>ON=破真空</t>
         </is>
       </c>
-      <c r="E54" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F54" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅/需突波吸收</t>
-        </is>
-      </c>
-      <c r="G54" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM1</t>
-        </is>
-      </c>
-      <c r="H54" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0020</t>
-        </is>
-      </c>
-      <c r="I54" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J54" s="16" t="inlineStr"/>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>儲存盒釋放；使用本列正式點位</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="inlineStr">
+      <c r="A55" s="17" t="inlineStr">
         <is>
           <t>Y0021</t>
         </is>
       </c>
-      <c r="B55" s="16" t="inlineStr">
-        <is>
-          <t>上機盒真空ON</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>上機盒真空ON(Relay)</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D55" s="16" t="inlineStr">
+      <c r="D55" s="17" t="inlineStr">
         <is>
           <t>ON=真空</t>
         </is>
       </c>
-      <c r="E55" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F55" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅/需突波吸收</t>
-        </is>
-      </c>
-      <c r="G55" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM1</t>
-        </is>
-      </c>
-      <c r="H55" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0021</t>
-        </is>
-      </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J55" s="16" t="inlineStr"/>
+      <c r="E55" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>上機盒吸附</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="inlineStr">
+      <c r="A56" s="17" t="inlineStr">
         <is>
           <t>Y0022</t>
         </is>
       </c>
-      <c r="B56" s="16" t="inlineStr">
-        <is>
-          <t>上機盒破真空</t>
-        </is>
-      </c>
-      <c r="C56" s="16" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>上機盒破真空(Relay)</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D56" s="16" t="inlineStr">
+      <c r="D56" s="17" t="inlineStr">
         <is>
           <t>ON=破真空</t>
         </is>
       </c>
-      <c r="E56" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F56" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅/需突波吸收</t>
-        </is>
-      </c>
-      <c r="G56" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM1</t>
-        </is>
-      </c>
-      <c r="H56" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0022</t>
-        </is>
-      </c>
-      <c r="I56" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J56" s="16" t="inlineStr"/>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>上機盒釋放；使用本列正式點位</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="inlineStr">
+      <c r="A57" s="17" t="inlineStr">
         <is>
           <t>Y0023</t>
         </is>
       </c>
-      <c r="B57" s="16" t="inlineStr">
-        <is>
-          <t>靜電消除器停止</t>
-        </is>
-      </c>
-      <c r="C57" s="16" t="inlineStr">
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>靜電消除器停止(Relay)</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D57" s="16" t="inlineStr">
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>ON=停止/Disable</t>
         </is>
       </c>
-      <c r="E57" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT/乾接點依手冊</t>
-        </is>
-      </c>
-      <c r="F57" s="16" t="inlineStr">
-        <is>
-          <t>需確認DTY-ELK01</t>
-        </is>
-      </c>
-      <c r="G57" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM2</t>
-        </is>
-      </c>
-      <c r="H57" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0023</t>
-        </is>
-      </c>
-      <c r="I57" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J57" s="16" t="inlineStr">
-        <is>
-          <t>依實際接線確認Enable或Stop語意。</t>
+      <c r="E57" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F57" s="17" t="inlineStr">
+        <is>
+          <t>靜電消除控制</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="inlineStr">
+      <c r="A58" s="17" t="inlineStr">
         <is>
           <t>Y0024</t>
         </is>
       </c>
-      <c r="B58" s="16" t="inlineStr">
-        <is>
-          <t>FFU電源ON</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="inlineStr">
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>FFU電源ON(Relay)</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D58" s="16" t="inlineStr">
+      <c r="D58" s="17" t="inlineStr">
         <is>
           <t>ON=FFU供電</t>
         </is>
       </c>
-      <c r="E58" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F58" s="16" t="inlineStr">
-        <is>
-          <t>驅動接觸器</t>
-        </is>
-      </c>
-      <c r="G58" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM2</t>
-        </is>
-      </c>
-      <c r="H58" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0024</t>
-        </is>
-      </c>
-      <c r="I58" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J58" s="16" t="inlineStr">
-        <is>
-          <t>不可直接切AC負載。</t>
+      <c r="E58" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>FFU電源控制</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="inlineStr">
+      <c r="A59" s="17" t="inlineStr">
         <is>
           <t>Y0034</t>
         </is>
       </c>
-      <c r="B59" s="16" t="inlineStr">
-        <is>
-          <t>三色燈-紅</t>
-        </is>
-      </c>
-      <c r="C59" s="16" t="inlineStr">
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>三色燈-紅(Relay)</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D59" s="16" t="inlineStr">
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>ON=紅燈</t>
         </is>
       </c>
-      <c r="E59" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F59" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅</t>
-        </is>
-      </c>
-      <c r="G59" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM2</t>
-        </is>
-      </c>
-      <c r="H59" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0034</t>
-        </is>
-      </c>
-      <c r="I59" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J59" s="16" t="inlineStr"/>
+      <c r="E59" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F59" s="17" t="inlineStr">
+        <is>
+          <t>Alarm</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="inlineStr">
+      <c r="A60" s="17" t="inlineStr">
         <is>
           <t>Y0035</t>
         </is>
       </c>
-      <c r="B60" s="16" t="inlineStr">
-        <is>
-          <t>三色燈-黃</t>
-        </is>
-      </c>
-      <c r="C60" s="16" t="inlineStr">
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>三色燈-黃(Relay)</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D60" s="16" t="inlineStr">
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>ON=黃燈</t>
         </is>
       </c>
-      <c r="E60" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F60" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅</t>
-        </is>
-      </c>
-      <c r="G60" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM2</t>
-        </is>
-      </c>
-      <c r="H60" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0035</t>
-        </is>
-      </c>
-      <c r="I60" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J60" s="16" t="inlineStr"/>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>Warning/Manual</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="inlineStr">
+      <c r="A61" s="17" t="inlineStr">
         <is>
           <t>Y0036</t>
         </is>
       </c>
-      <c r="B61" s="16" t="inlineStr">
-        <is>
-          <t>三色燈-綠</t>
-        </is>
-      </c>
-      <c r="C61" s="16" t="inlineStr">
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>三色燈-綠(Relay)</t>
+        </is>
+      </c>
+      <c r="C61" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D61" s="16" t="inlineStr">
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>ON=綠燈</t>
         </is>
       </c>
-      <c r="E61" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F61" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅</t>
-        </is>
-      </c>
-      <c r="G61" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM2</t>
-        </is>
-      </c>
-      <c r="H61" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0036</t>
-        </is>
-      </c>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J61" s="16" t="inlineStr"/>
+      <c r="E61" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>Ready/Auto Run</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="inlineStr">
+      <c r="A62" s="17" t="inlineStr">
         <is>
           <t>Y0037</t>
         </is>
       </c>
-      <c r="B62" s="16" t="inlineStr">
-        <is>
-          <t>三色燈-蜂鳴器</t>
-        </is>
-      </c>
-      <c r="C62" s="16" t="inlineStr">
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>三色燈-蜂鳴器(Relay)</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D62" s="16" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>ON=蜂鳴</t>
         </is>
       </c>
-      <c r="E62" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F62" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅</t>
-        </is>
-      </c>
-      <c r="G62" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM2</t>
-        </is>
-      </c>
-      <c r="H62" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0037</t>
-        </is>
-      </c>
-      <c r="I62" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J62" s="16" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t>X0044</t>
-        </is>
-      </c>
-      <c r="B63" s="16" t="inlineStr">
-        <is>
-          <t>Z檢查站_左右定位伸出完成</t>
-        </is>
-      </c>
-      <c r="C63" s="16" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="D63" s="16" t="inlineStr">
-        <is>
-          <t>ON=伸出完成</t>
-        </is>
-      </c>
-      <c r="E63" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F63" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G63" s="16" t="inlineStr">
-        <is>
-          <t>擴充DI-COM</t>
-        </is>
-      </c>
-      <c r="H63" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0044</t>
-        </is>
-      </c>
-      <c r="I63" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J63" s="16" t="inlineStr">
-        <is>
-          <t>左右2支定位氣缸伸出回授串/並接後進PLC；兩支皆伸出才ON。</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="16" t="inlineStr">
-        <is>
-          <t>X0045</t>
-        </is>
-      </c>
-      <c r="B64" s="16" t="inlineStr">
-        <is>
-          <t>Z檢查站_左右定位縮回完成</t>
-        </is>
-      </c>
-      <c r="C64" s="16" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="D64" s="16" t="inlineStr">
-        <is>
-          <t>ON=縮回完成</t>
-        </is>
-      </c>
-      <c r="E64" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F64" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G64" s="16" t="inlineStr">
-        <is>
-          <t>擴充DI-COM</t>
-        </is>
-      </c>
-      <c r="H64" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0045</t>
-        </is>
-      </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J64" s="16" t="inlineStr">
-        <is>
-          <t>左右2支定位氣缸縮回完成。</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="16" t="inlineStr">
-        <is>
-          <t>X0046</t>
-        </is>
-      </c>
-      <c r="B65" s="16" t="inlineStr">
-        <is>
-          <t>Z檢查站_前後定位伸出完成</t>
-        </is>
-      </c>
-      <c r="C65" s="16" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="D65" s="16" t="inlineStr">
-        <is>
-          <t>ON=伸出完成</t>
-        </is>
-      </c>
-      <c r="E65" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F65" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G65" s="16" t="inlineStr">
-        <is>
-          <t>擴充DI-COM</t>
-        </is>
-      </c>
-      <c r="H65" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0046</t>
-        </is>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J65" s="16" t="inlineStr">
-        <is>
-          <t>前後2支定位氣缸伸出完成。</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="16" t="inlineStr">
-        <is>
-          <t>X0047</t>
-        </is>
-      </c>
-      <c r="B66" s="16" t="inlineStr">
-        <is>
-          <t>Z檢查站_前後定位縮回完成</t>
-        </is>
-      </c>
-      <c r="C66" s="16" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="D66" s="16" t="inlineStr">
-        <is>
-          <t>ON=縮回完成</t>
-        </is>
-      </c>
-      <c r="E66" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F66" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G66" s="16" t="inlineStr">
-        <is>
-          <t>擴充DI-COM</t>
-        </is>
-      </c>
-      <c r="H66" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0047</t>
-        </is>
-      </c>
-      <c r="I66" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J66" s="16" t="inlineStr">
-        <is>
-          <t>前後2支定位氣缸縮回完成。</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="16" t="inlineStr">
-        <is>
-          <t>X0050</t>
-        </is>
-      </c>
-      <c r="B67" s="16" t="inlineStr">
-        <is>
-          <t>安全門_關閉回授</t>
-        </is>
-      </c>
-      <c r="C67" s="16" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="D67" s="16" t="inlineStr">
-        <is>
-          <t>ON=門關閉</t>
-        </is>
-      </c>
-      <c r="E67" s="16" t="inlineStr">
-        <is>
-          <t>安全輔助/24V</t>
-        </is>
-      </c>
-      <c r="F67" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G67" s="16" t="inlineStr">
-        <is>
-          <t>擴充DI-COM</t>
-        </is>
-      </c>
-      <c r="H67" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0050</t>
-        </is>
-      </c>
-      <c r="I67" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J67" s="16" t="inlineStr">
-        <is>
-          <t>PLC監看用，安全功能仍走安全繼電器。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="16" t="inlineStr">
-        <is>
-          <t>X0051</t>
-        </is>
-      </c>
-      <c r="B68" s="16" t="inlineStr">
-        <is>
-          <t>安全門_鎖定回授</t>
-        </is>
-      </c>
-      <c r="C68" s="16" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="D68" s="16" t="inlineStr">
-        <is>
-          <t>ON=門鎖定</t>
-        </is>
-      </c>
-      <c r="E68" s="16" t="inlineStr">
-        <is>
-          <t>安全輔助/24V</t>
-        </is>
-      </c>
-      <c r="F68" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G68" s="16" t="inlineStr">
-        <is>
-          <t>擴充DI-COM</t>
-        </is>
-      </c>
-      <c r="H68" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0051</t>
-        </is>
-      </c>
-      <c r="I68" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J68" s="16" t="inlineStr">
-        <is>
-          <t>PLC監看門鎖狀態。</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="16" t="inlineStr">
-        <is>
-          <t>X0052</t>
-        </is>
-      </c>
-      <c r="B69" s="16" t="inlineStr">
-        <is>
-          <t>儲存盒盒蓋關閉</t>
-        </is>
-      </c>
-      <c r="C69" s="16" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="D69" s="16" t="inlineStr">
-        <is>
-          <t>ON=盒蓋關閉</t>
-        </is>
-      </c>
-      <c r="E69" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F69" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G69" s="16" t="inlineStr">
-        <is>
-          <t>擴充DI-COM</t>
-        </is>
-      </c>
-      <c r="H69" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0052</t>
-        </is>
-      </c>
-      <c r="I69" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J69" s="16" t="inlineStr">
-        <is>
-          <t>完成流程後才允許儲存盒破真空/取盒。</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="16" t="inlineStr">
-        <is>
-          <t>X0053</t>
-        </is>
-      </c>
-      <c r="B70" s="16" t="inlineStr">
-        <is>
-          <t>上機盒盒蓋關閉</t>
-        </is>
-      </c>
-      <c r="C70" s="16" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="D70" s="16" t="inlineStr">
-        <is>
-          <t>ON=盒蓋關閉</t>
-        </is>
-      </c>
-      <c r="E70" s="16" t="inlineStr">
-        <is>
-          <t>24V ON</t>
-        </is>
-      </c>
-      <c r="F70" s="16" t="inlineStr">
-        <is>
-          <t>NPN輸入/漏型PLC</t>
-        </is>
-      </c>
-      <c r="G70" s="16" t="inlineStr">
-        <is>
-          <t>擴充DI-COM</t>
-        </is>
-      </c>
-      <c r="H70" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0053</t>
-        </is>
-      </c>
-      <c r="I70" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J70" s="16" t="inlineStr">
-        <is>
-          <t>完成流程後才允許上機盒破真空/取盒。</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="16" t="inlineStr">
-        <is>
-          <t>Y0025</t>
-        </is>
-      </c>
-      <c r="B71" s="16" t="inlineStr">
-        <is>
-          <t>Z檢查站_左右定位電磁閥</t>
-        </is>
-      </c>
-      <c r="C71" s="16" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="D71" s="16" t="inlineStr">
-        <is>
-          <t>ON=定位伸出</t>
-        </is>
-      </c>
-      <c r="E71" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F71" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅/需突波吸收</t>
-        </is>
-      </c>
-      <c r="G71" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM2</t>
-        </is>
-      </c>
-      <c r="H71" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0025</t>
-        </is>
-      </c>
-      <c r="I71" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J71" s="16" t="inlineStr">
-        <is>
-          <t>控制左右2支定位氣缸，同組動作。</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="16" t="inlineStr">
-        <is>
-          <t>Y0026</t>
-        </is>
-      </c>
-      <c r="B72" s="16" t="inlineStr">
-        <is>
-          <t>Z檢查站_前後定位電磁閥</t>
-        </is>
-      </c>
-      <c r="C72" s="16" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="D72" s="16" t="inlineStr">
-        <is>
-          <t>ON=定位伸出</t>
-        </is>
-      </c>
-      <c r="E72" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F72" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅/需突波吸收</t>
-        </is>
-      </c>
-      <c r="G72" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM2</t>
-        </is>
-      </c>
-      <c r="H72" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0026</t>
-        </is>
-      </c>
-      <c r="I72" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J72" s="16" t="inlineStr">
-        <is>
-          <t>控制前後2支定位氣缸，同組動作。</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="16" t="inlineStr">
-        <is>
-          <t>Y0027</t>
-        </is>
-      </c>
-      <c r="B73" s="16" t="inlineStr">
-        <is>
-          <t>安全門解鎖請求</t>
-        </is>
-      </c>
-      <c r="C73" s="16" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="D73" s="16" t="inlineStr">
-        <is>
-          <t>ON=請求解鎖</t>
-        </is>
-      </c>
-      <c r="E73" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F73" s="16" t="inlineStr">
-        <is>
-          <t>至安全控制/門鎖控制</t>
-        </is>
-      </c>
-      <c r="G73" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM2</t>
-        </is>
-      </c>
-      <c r="H73" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0027</t>
-        </is>
-      </c>
-      <c r="I73" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J73" s="16" t="inlineStr">
-        <is>
-          <t>PLC只送請求，不旁路安全。</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="16" t="inlineStr">
-        <is>
-          <t>Y0030</t>
-        </is>
-      </c>
-      <c r="B74" s="16" t="inlineStr">
-        <is>
-          <t>儲存盒破真空</t>
-        </is>
-      </c>
-      <c r="C74" s="16" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="D74" s="16" t="inlineStr">
-        <is>
-          <t>ON=破真空</t>
-        </is>
-      </c>
-      <c r="E74" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F74" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅/需突波吸收</t>
-        </is>
-      </c>
-      <c r="G74" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM2</t>
-        </is>
-      </c>
-      <c r="H74" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0030</t>
-        </is>
-      </c>
-      <c r="I74" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J74" s="16" t="inlineStr">
-        <is>
-          <t>盒蓋關閉後才允許。</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="16" t="inlineStr">
-        <is>
-          <t>Y0031</t>
-        </is>
-      </c>
-      <c r="B75" s="16" t="inlineStr">
-        <is>
-          <t>上機盒破真空</t>
-        </is>
-      </c>
-      <c r="C75" s="16" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="D75" s="16" t="inlineStr">
-        <is>
-          <t>ON=破真空</t>
-        </is>
-      </c>
-      <c r="E75" s="16" t="inlineStr">
-        <is>
-          <t>24V OUT</t>
-        </is>
-      </c>
-      <c r="F75" s="16" t="inlineStr">
-        <is>
-          <t>晶體輸出可直驅/需突波吸收</t>
-        </is>
-      </c>
-      <c r="G75" s="16" t="inlineStr">
-        <is>
-          <t>DO-COM2</t>
-        </is>
-      </c>
-      <c r="H75" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0031</t>
-        </is>
-      </c>
-      <c r="I75" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-      <c r="J75" s="16" t="inlineStr">
-        <is>
-          <t>盒蓋關閉後才允許。</t>
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>已定正式點位</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>Alarm buzzer</t>
         </is>
       </c>
     </row>
@@ -14657,6 +12593,189 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>原因</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>處理方式</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>不可使用點位</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Z檢查站左右定位</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>正式點位已存在</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>使用 X0016/X0017、Y0011/Y0012</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>流程改用既有點位</t>
+        </is>
+      </c>
+      <c r="E2" s="17" t="inlineStr">
+        <is>
+          <t>不得新增 X0044/X0045/Y0025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Z檢查站前後定位</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>正式點位已存在</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>使用 X0020/X0021、Y0013/Y0014</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>流程改用既有點位</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>不得新增 X0046/X0047/Y0026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>安全門門鎖回授</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>待設計，不佔用正式X/Y</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>BOM/PLC表未定正式點位</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>放入安全設計備註；若業主要求PLC監看再擴充I/O</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>不得暫塞 X0050/X0051</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>儲存盒/上機盒盒蓋</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>使用現有開蓋定位</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>X0023/X0025已存在</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>不得另增盒蓋關閉點位，除非機構/業主另要求</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>不得暫塞 X0052/X0053</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>儲存盒/上機盒破真空</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>正式點位已存在</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Y0020/Y0022已存在</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>流程改用既有點位</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>不得新增 Y0030/Y0031</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -14680,11 +12799,11 @@
           <t>03_M共用_HMI_Barcode</t>
         </is>
       </c>
-      <c r="B1" s="14" t="n"/>
-      <c r="C1" s="14" t="n"/>
-      <c r="D1" s="14" t="n"/>
-      <c r="E1" s="14" t="n"/>
-      <c r="F1" s="14" t="n"/>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="21" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
@@ -19143,11 +17262,11 @@
           <t>06_M軸3_Z升降</t>
         </is>
       </c>
-      <c r="B1" s="14" t="n"/>
-      <c r="C1" s="14" t="n"/>
-      <c r="D1" s="14" t="n"/>
-      <c r="E1" s="14" t="n"/>
-      <c r="F1" s="14" t="n"/>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="21" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
@@ -19884,11 +18003,11 @@
           <t>07_M軸4_Z旋轉</t>
         </is>
       </c>
-      <c r="B1" s="14" t="n"/>
-      <c r="C1" s="14" t="n"/>
-      <c r="D1" s="14" t="n"/>
-      <c r="E1" s="14" t="n"/>
-      <c r="F1" s="14" t="n"/>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="21" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
@@ -20633,11 +18752,11 @@
           <t>08_D資料參數</t>
         </is>
       </c>
-      <c r="B1" s="14" t="n"/>
-      <c r="C1" s="14" t="n"/>
-      <c r="D1" s="14" t="n"/>
-      <c r="E1" s="14" t="n"/>
-      <c r="F1" s="14" t="n"/>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="21" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="15" t="inlineStr">

--- a/docs/PTC_Mask_Transfer_4Axis_Design_Draft.xlsx
+++ b/docs/PTC_Mask_Transfer_4Axis_Design_Draft.xlsx
@@ -34,6 +34,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_HMI_4軸畫面" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_4軸CODEX封口清單" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_IO不可新增與待確認" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_IO補充_雙線圈版" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_雙線圈控制標準" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -2716,16 +2718,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2756,6 +2758,11 @@
       </c>
       <c r="F1" s="14" t="inlineStr">
         <is>
+          <t>互鎖/安全</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
           <t>備註</t>
         </is>
       </c>
@@ -2788,7 +2795,12 @@
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>Auto只允許Axis1/2/3；Axis4不參與</t>
+          <t>Axis4 Auto禁止</t>
+        </is>
+      </c>
+      <c r="G2" s="16" t="inlineStr">
+        <is>
+          <t>Auto只允許Axis1/2/3</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2817,7 @@
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>Y0011 ON、Y0012 OFF</t>
+          <t>Y0011 ON；Y0012 OFF</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -2815,12 +2827,17 @@
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
-          <t>Timeout K310</t>
+          <t>K310</t>
         </is>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>使用既有正式點位，不新增Y0025/X0044</t>
+          <t>Y0011/Y0012互斥</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>左右2支伸出磁簧串聯後才完成</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2854,7 @@
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>Y0013 ON、Y0014 OFF</t>
+          <t>Y0013 ON；Y0014 OFF</t>
         </is>
       </c>
       <c r="D4" s="16" t="inlineStr">
@@ -2847,12 +2864,17 @@
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
-          <t>Timeout K311</t>
+          <t>K311</t>
         </is>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>使用既有正式點位，不新增Y0026/X0046</t>
+          <t>Y0013/Y0014互斥</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>前後2支伸出磁簧串聯後才完成</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2901,17 @@
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
-          <t>K312 光罩不在席</t>
+          <t>K312</t>
         </is>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
-          <t>Z升起前必要條件</t>
+          <t>若X0026 OFF禁止Z上升</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>Z升降前必要條件</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2933,7 @@
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>M4551 ON + Busy OFF + 誤差&lt;=D4504</t>
+          <t>M4551 ON + M4527 Busy OFF + M4518 Alarm OFF + 誤差&lt;=D4504</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
@@ -2916,7 +2943,12 @@
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>平台位高度現場實測</t>
+          <t>啟動前再確認X0016+X0020+X0026+M4517</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>平台位高度現場Teach</t>
         </is>
       </c>
     </row>
@@ -2933,12 +2965,12 @@
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>Y0011 OFF、Y0012 ON、Y0013 OFF、Y0014 ON</t>
+          <t>Y0011 OFF；Y0012 ON；Y0013 OFF；Y0014 ON</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>X0017 ON 且 X0021 ON</t>
+          <t>X0017 AND X0021</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
@@ -2948,7 +2980,12 @@
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
-          <t>定位縮回後才可進Barcode高度</t>
+          <t>Y0011/Y0012不可同時ON；Y0013/Y0014不可同時ON</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>未全部縮回不可進Barcode位</t>
         </is>
       </c>
     </row>
@@ -2970,7 +3007,7 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>M4552 ON + Busy OFF + 誤差&lt;=D4504</t>
+          <t>M4552 ON + M4527 Busy OFF + M4518 Alarm OFF + 誤差&lt;=D4504</t>
         </is>
       </c>
       <c r="E8" s="16" t="inlineStr">
@@ -2980,7 +3017,12 @@
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>Barcode高度現場實測</t>
+          <t>定位縮回完成才允許</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>Barcode高度現場Teach</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3054,12 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>KEYENCE SR-2000W；通訊格式需實測</t>
+          <t>通訊Timeout需停在S389</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>Barcode型號依BOM/採購版統一；若目前BOM為SR-1000W，文件先以SR-1000W</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3076,7 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>PLC/HMI比對D6300~D6349與D6350~D6399</t>
+          <t>比較Storage Barcode與Mask Barcode</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
@@ -3044,7 +3091,12 @@
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>Barcode OFF 記錄BYPASS</t>
+          <t>NG不得直接PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>Barcode OFF記錄BYPASS</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3128,12 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>HMI彈窗，不需要操作紀錄</t>
+          <t>Popup Hold</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>NG返回來源盒</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3145,7 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>Z升降回安全/原點等待位</t>
+          <t>Z升降回Home</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -3098,7 +3155,7 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>M4550或M4553 ON + Busy OFF</t>
+          <t>M4550 Home Complete + M4527 Busy OFF + M4518 Alarm OFF</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr">
@@ -3108,7 +3165,12 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>完成後通知X回檢查位</t>
+          <t>固定回Home，不用M4553替代</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>需求若改安全等待位再另定</t>
         </is>
       </c>
     </row>
@@ -3133,8 +3195,17 @@
           <t>主流程收到M6103</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr"/>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>X軸才可回Inspection</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>M6103=Z/Barcode流程完成且Z升降在安全位</t>
         </is>
@@ -3158,7 +3229,7 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>X軸完成回放</t>
+          <t>X軸回放完成</t>
         </is>
       </c>
       <c r="E14" s="16" t="inlineStr">
@@ -3168,7 +3239,12 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>不得自動轉Axis4</t>
+          <t>Axis4不動作</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>Barcode/Visual NG共同回收</t>
         </is>
       </c>
     </row>
@@ -3193,8 +3269,17 @@
           <t>HMI排除後回初始化/安全位</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr"/>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>所有定位閥不可同時ON</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>停機或警告依Alarm表</t>
         </is>
@@ -6476,7 +6561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6960,6 +7045,210 @@
           <t>依業主標準決定等級。</t>
         </is>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Z定位雙線圈互鎖異常</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>停機</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Y0011/Y0012或Y0013/Y0014同時ON</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>立即RST同組輸出並Alarm</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>K360</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>需檢查PLC程式/HMI手動按鈕互鎖</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="16" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Z定位伸出Timeout</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>停機</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>S301/S302未於時間內達X0016/X0020</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>停止Z流程，保持/切除依氣路策略</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>K310/K311</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>檢查氣壓、磁簧、閥線圈</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="16" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Z定位縮回Timeout</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>停機</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>S305未於時間內達X0017 AND X0021</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>禁止Z移到Barcode位</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>K321</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>檢查機構干涉與閥線圈</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="16" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Z定位雙線圈互鎖異常</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>停機</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Y0011/Y0012或Y0013/Y0014同時ON</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>立即RST同組輸出並Alarm</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>K360</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>需檢查PLC程式/HMI手動按鈕互鎖</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="16" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Z定位伸出Timeout</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>停機</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>S301/S302未於時間內達X0016/X0020</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>停止Z流程，保持/切除依氣路策略</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>K310/K311</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>檢查氣壓、磁簧、閥線圈</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="16" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Z定位縮回Timeout</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>停機</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>S305未於時間內達X0017 AND X0021</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>禁止Z移到Barcode位</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>K321</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>檢查機構干涉與閥線圈</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="n"/>
+      <c r="H18" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8626,47 +8915,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>Seq</t>
+          <t>No</t>
         </is>
       </c>
       <c r="B1" s="14" t="inlineStr">
         <is>
-          <t>流程</t>
+          <t>流程段</t>
         </is>
       </c>
       <c r="C1" s="14" t="inlineStr">
         <is>
-          <t>動作</t>
+          <t>主要動作</t>
         </is>
       </c>
       <c r="D1" s="14" t="inlineStr">
         <is>
-          <t>條件/回授</t>
+          <t>使用軸/輸出</t>
         </is>
       </c>
       <c r="E1" s="14" t="inlineStr">
         <is>
-          <t>異常</t>
+          <t>完成條件</t>
         </is>
       </c>
       <c r="F1" s="14" t="inlineStr">
         <is>
-          <t>M/D/IO</t>
+          <t>異常處理</t>
         </is>
       </c>
       <c r="G1" s="14" t="inlineStr">
@@ -8686,27 +8975,27 @@
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>Safety/Air/FFU/Init/Axis Ready/Material State/功能Enable檢查。</t>
+          <t>確認Safety/Air/FFU/初始化/Barcode條件</t>
         </is>
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>Barcode Enable ON時M6301必須ON。</t>
+          <t>X0000/X0001/X0036/X0037/M1125/M1225/M1425</t>
         </is>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
-          <t>任一不成立禁止Start</t>
+          <t>Ready成立</t>
         </is>
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>X0000/X0001/M6300/M6301</t>
+          <t>不成立禁止啟動</t>
         </is>
       </c>
       <c r="G2" s="16" t="inlineStr">
         <is>
-          <t>Safety/Air/FFU不可Bypass。</t>
+          <t>Barcode Enable ON時需Storage Barcode Valid</t>
         </is>
       </c>
     </row>
@@ -8716,32 +9005,32 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>X取來源</t>
+          <t>X取來源盒</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>X橫移到來源，X升降下降，夾爪Close，真空ON。</t>
+          <t>X橫移到來源位，X升降到取片位，夾爪關，真空ON</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>夾爪Close + Vacuum OK，真空位二次確認。</t>
+          <t>Axis1/Axis2/Y0010/Y0015</t>
         </is>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
-          <t>K180/K200</t>
+          <t>X0015+X0027</t>
         </is>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>S100/S150/S200</t>
+          <t>真空NG-&gt;S189/S299</t>
         </is>
       </c>
       <c r="G3" s="16" t="inlineStr">
         <is>
-          <t>正向來源Storage；反向來源Load。</t>
+          <t>正向來源=儲存盒；反向來源=上機盒</t>
         </is>
       </c>
     </row>
@@ -8751,61 +9040,69 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>X移Inspection</t>
+          <t>X真空確認上升</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>X升降上位，X橫移到Inspection，X升降下降。</t>
+          <t>上升約10mm到真空確認位，再確認真空OK</t>
         </is>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>X到Inspection且X升降到放/取位。</t>
+          <t>Axis2/M4330</t>
         </is>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
-          <t>K150/K160</t>
+          <t>X0027保持ON</t>
         </is>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>M4151/M435x</t>
-        </is>
-      </c>
-      <c r="G4" s="16" t="inlineStr"/>
+          <t>真空掉落停機</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>確認後升到上位</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="n">
+      <c r="A5" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>放到Inspection</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>破真空，夾爪Open，光罩在席確認。</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>X0026 ON。</t>
-        </is>
-      </c>
-      <c r="E5" s="19" t="inlineStr">
-        <is>
-          <t>K201/K230</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>X0026/Y0016</t>
-        </is>
-      </c>
-      <c r="G5" s="19" t="inlineStr"/>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>X移到檢查位</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>X升降上位後，X橫移到檢查位</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Axis1</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>M4151 ON</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Axis Alarm停機</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>到位後才下降</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="n">
@@ -8813,32 +9110,32 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>X離開Clear</t>
+          <t>X放到檢查站</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>X升降上位，X橫移離開檢查干涉區。</t>
+          <t>X升降到檢查放位，破真空，夾爪開</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>X安全位到位後才SET M6100。</t>
+          <t>Axis2/Y0016/Y0007</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>K171</t>
+          <t>X0014+X0026</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>M6100</t>
+          <t>光罩未在席-&gt;Alarm</t>
         </is>
       </c>
       <c r="G6" s="16" t="inlineStr">
         <is>
-          <t>保護Z軸不撞。</t>
+          <t>放完X回上位再離開干涉區</t>
         </is>
       </c>
     </row>
@@ -8848,32 +9145,32 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>Z定位與Barcode</t>
+          <t>X離開檢查位</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>左右定位伸出、前後定位伸出、Z到Platform、定位縮回、Z到Barcode。</t>
+          <t>X升降回上位，X橫移離開檢查區</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>X0044/X0046/X0045/X0047/M4551/M4552。</t>
+          <t>Axis1/Axis2</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>K180/K240</t>
+          <t>X已Clear</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
-          <t>S300</t>
+          <t>未Clear禁止Z</t>
         </is>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
-          <t>Axis3自動。</t>
+          <t>避免Z軸動作干涉</t>
         </is>
       </c>
     </row>
@@ -8883,102 +9180,102 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>Barcode Compare</t>
+          <t>Z左右定位伸出</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>SR-2000W讀取Mask Barcode並比對Storage Barcode。</t>
+          <t>左右雙線圈閥伸出</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>M6304 OK；NG進Return。</t>
+          <t>Y0011 ON/Y0012 OFF</t>
         </is>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>K181/K182</t>
+          <t>X0016 ON</t>
         </is>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>D6300/D6350/D6400</t>
+          <t>K310</t>
         </is>
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
-          <t>Barcode OFF則BYPASS記錄。</t>
+          <t>2支磁簧串聯</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>Visual確認</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>若Visual Enable ON，HMI彈窗人工OK/NG。</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>M6502 OK；M6503 NG進Return。</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>K260</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>M6500~M6504/D6500</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>Visual OFF則BYPASS。</t>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Z前後定位伸出</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>前後雙線圈閥伸出</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Y0013 ON/Y0014 OFF</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>X0020 ON</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>K311</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>2支磁簧串聯</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="n">
+      <c r="A10" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>Z回安全</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>Z回Home/安全等待位。</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>M4550/M4553 ON後SET M6103。</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>K240</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>M6103</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
-        <is>
-          <t>X才可進檢查位。</t>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Z升平台位</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>確認X0026後Z升到平台位</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>Axis3/M4521/D4514</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>M4551 ON</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>K320</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>啟動前需X0016+X0020+X0026</t>
         </is>
       </c>
     </row>
@@ -8988,30 +9285,34 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>X取Inspection</t>
+          <t>Z定位縮回</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>X回Inspection，夾爪Close，真空ON，升降上位。</t>
+          <t>左右/前後雙線圈閥縮回</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Vacuum OK + M4350。</t>
+          <t>Y0012 ON/Y0014 ON</t>
         </is>
       </c>
       <c r="E11" s="16" t="inlineStr">
         <is>
-          <t>K200/K160</t>
+          <t>X0017 AND X0021</t>
         </is>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>S131/S163</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr"/>
+          <t>K321</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>縮回後才可去Barcode</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="n">
@@ -9019,92 +9320,104 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>PASS目的地放片</t>
+          <t>Z到Barcode位</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>正向放Load；反向放Storage。</t>
+          <t>Z升降到掃碼高度</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>放片完成。</t>
+          <t>Axis3/M4522/D4510</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
-          <t>K201</t>
+          <t>M4552 ON</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>S141/S171</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr"/>
+          <t>K322</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>高度現場Teach</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>NG Return</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>正向NG回Storage；反向NG回Load。</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>Return放片完成。</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>K201</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>S380後接X Return</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>不得Pass到目的地。</t>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Barcode/Visual</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>掃碼、比對、目視檢查選配</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>M630x/M650x</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>OK/BYPASS</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>NG-&gt;回來源盒</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>Axis4不參與Auto</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="n">
+      <c r="A14" s="16" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Cycle Complete Popup</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>HMI顯示流程完成，允許開門。</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>M6600 ON。</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr"/>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>M6600/M6601/Y0027</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr"/>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Z回Home</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>Z升降回Home</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>Axis3/M4520/D4512</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>M4550 ON</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>K350</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>固定Home Complete</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="n">
@@ -9112,32 +9425,32 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>盒蓋關閉後破真空</t>
+          <t>X回檢查位取片</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>Storage Lid/Load Lid Closed後破真空。</t>
+          <t>X回檢查位，下降取片，真空確認，上升</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>X0052/X0053 ON。</t>
+          <t>Axis1/Axis2/Y0010/Y0015</t>
         </is>
       </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
-          <t>K201</t>
+          <t>X0027 ON</t>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>Y0030/Y0031</t>
+          <t>真空NG停機</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
         <is>
-          <t>兩盒獨立判斷。</t>
+          <t>準備送目的盒</t>
         </is>
       </c>
     </row>
@@ -9147,28 +9460,67 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>取出兩盒完成</t>
+          <t>X送目的盒</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Storage Box Present OFF + Load Box Present OFF。</t>
+          <t>PASS送目的盒；NG回來源盒</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>X0022 OFF + X0024 OFF。</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr"/>
+          <t>Axis1/Axis2/Y0016/Y0007</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>放片完成</t>
+        </is>
+      </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>M6604/D6600</t>
+          <t>未到位/真空異常停機</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
-          <t>回Ready。</t>
+          <t>正反向依D6100/M6002/M6003</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Cycle Complete</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>允許開門/移除盒，等待兩盒移除</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>M6600/Y0020/Y0022/X0022/X0024</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>X0022 OFF AND X0024 OFF</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>逾時警告</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="inlineStr">
+        <is>
+          <t>不新增門鎖X/Y，門鎖若需PLC監看另走擴充點位</t>
         </is>
       </c>
     </row>
@@ -12215,15 +12567,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="74" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12234,355 +12586,385 @@
       </c>
       <c r="B1" s="14" t="inlineStr">
         <is>
-          <t>等級</t>
+          <t>優先級</t>
         </is>
       </c>
       <c r="C1" s="14" t="inlineStr">
         <is>
-          <t>項目</t>
+          <t>確認/修改事項</t>
         </is>
       </c>
       <c r="D1" s="14" t="inlineStr">
         <is>
-          <t>判定</t>
+          <t>CODEX結果</t>
         </is>
       </c>
       <c r="E1" s="14" t="inlineStr">
         <is>
-          <t>設計處理</t>
+          <t>理由/替代方案</t>
         </is>
       </c>
       <c r="F1" s="14" t="inlineStr">
         <is>
-          <t>位置</t>
+          <t>實際修改位置</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="n">
+      <c r="A2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>2軸版升級為4軸完整定義</t>
-        </is>
-      </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>正式X/Y點位不可任意新增</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
-        <is>
-          <t>Axis1~4 M/D/S/HMI架構已列。</t>
-        </is>
-      </c>
-      <c r="F2" s="16" t="inlineStr">
-        <is>
-          <t>00_4軸新設計總覽</t>
+      <c r="E2" s="17" t="inlineStr">
+        <is>
+          <t>02_XY點位表只保留BOM/PLC已定義點位</t>
+        </is>
+      </c>
+      <c r="F2" s="17" t="inlineStr">
+        <is>
+          <t>02_XY點位表</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>Auto只允許Axis1/2/3</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Z定位採4DI+4DO雙線圈版</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>Axis4明確手動限定，Auto禁止。</t>
-        </is>
-      </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>X0016/X0017/X0020/X0021 + Y0011/Y0012/Y0013/Y0014</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>01_IO補充_雙線圈版</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>廢止X0044~X0047、Y0025/Y0026舊方案</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>避免PLC/HMI/電路圖引用不同地址</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>01_IO補充_雙線圈版、26_IO不可新增與待確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>S301/S305左右雙線圈互斥</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>Y0011與Y0012不可同時ON</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>12_流程_Z升降_Barcode_S300</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>S302/S305前後雙線圈互斥</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>Y0013與Y0014不可同時ON</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>12_流程_Z升降_Barcode_S300</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Auto總流程改用正式Z定位點位</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>21表使用X0016/X0020/X0017/X0021</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>21_4軸Auto完整流程</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Axis4 Z旋轉Auto禁止</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>Axis4只允許工程/手動調機</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>13_流程_Z旋轉手動_S400</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>Axis3 Z升降Servo Device Map</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>Barcode型號與BOM統一</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>待確認</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>若BOM為SR-1000W，文件以SR-1000W；若採購改SR-2000W須同步BOM</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>12_S300、23_Barcode_History、BOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>S304啟動前再確認定位與光罩</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>M4517/M4518/M452x/M455x與D451x/D455x。</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>06_M軸3_Z升降 / 08_D資料參數</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Axis4 Manual Device Map</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>X0016+X0020+X0026+Axis3 Ready</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>12_流程_Z升降_Barcode_S300</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>S310固定回Home</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>M4717/M4718/M472x/M473x/M475x與D471x。</t>
-        </is>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>07_M軸4_Z旋轉 / 13_流程_Z旋轉手動_S400</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>Z定位氣缸4DI/2DO</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>完成條件只認M4550 Home Complete，不以M4553替代</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>12_流程_Z升降_Barcode_S300</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>Fault Output Matrix補雙線圈故障策略</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>X0044~X0047、Y0025~Y0026正式配置。</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>02_XY點位表 / 01_IO新增與配置</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Z完整Sequence</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>完成</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>LR定位、FB定位、Mask Presence、Platform、縮回、Barcode、Home。</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>12_流程_Z升降_Barcode_S300</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Barcode Enable與Storage Valid</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>完成</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>M6300/M6301與D6300起始區。</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>03_M共用_HMI_Barcode / 23_Barcode_History設計</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Visual Enable與人工判定</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>完成</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>M6500~M6504、D6500/D6502。</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>22_功能Enable矩陣 / 24_HMI_4軸畫面</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>Cycle Complete與取盒</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>完成</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>M6600~M6604、X0052/X0053、Y0030/Y0031。</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>21_4軸Auto完整流程</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>異常時禁止同組雙線圈同時ON，安全/氣壓異常依停機策略處理</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>18_Fault_Output_Matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>Barcode History 1000筆</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>設計完成/實作待HMI</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>建議用HMI Ring Buffer/Data Logging，不讓PLC搬移1000筆字串。</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>23_Barcode_History設計</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>現場Release</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>仍需SR-2000W、Z高度、Tolerance、氣缸、真空、安全策略實測。</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>需實測SR通訊、Z高度、Tolerance、Safety Stop、真空/煞車策略</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>16_驗收_Release_Gate</t>
         </is>
@@ -12768,6 +13150,644 @@
       <c r="E6" s="17" t="inlineStr">
         <is>
           <t>不得新增 Y0030/Y0031</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>分類</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>正式點位</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>硬體/接線定義</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>流程使用</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Z定位DI</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>X0016</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>左右定位伸出完成</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>左右2支氣缸伸出磁簧串聯後進PLC</t>
+        </is>
+      </c>
+      <c r="E2" s="17" t="inlineStr">
+        <is>
+          <t>S301完成條件</t>
+        </is>
+      </c>
+      <c r="F2" s="17" t="inlineStr">
+        <is>
+          <t>正式採用</t>
+        </is>
+      </c>
+      <c r="G2" s="17" t="inlineStr">
+        <is>
+          <t>ON=兩支皆伸出</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Z定位DI</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>X0017</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>左右定位縮回完成</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>左右2支氣缸縮回磁簧串聯後進PLC</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>S305完成條件</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>正式採用</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>ON=兩支皆縮回</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Z定位DI</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>X0020</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>前後定位伸出完成</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>前後2支氣缸伸出磁簧串聯後進PLC</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>S302完成條件</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>正式採用</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>ON=兩支皆伸出</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Z定位DI</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>X0021</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>前後定位縮回完成</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>前後2支氣缸縮回磁簧串聯後進PLC</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>S305完成條件</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>正式採用</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>ON=兩支皆縮回</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Z定位DO</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Y0011</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>左右定位伸出線圈</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>雙線圈閥A線圈</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>S301</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>正式採用</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>必須與Y0012互鎖，不可同時ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Z定位DO</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Y0012</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>左右定位縮回線圈</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>雙線圈閥B線圈</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>S305</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>正式採用</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>必須與Y0011互鎖，不可同時ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Z定位DO</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Y0013</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>前後定位伸出線圈</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>雙線圈閥A線圈</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>S302</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>正式採用</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>必須與Y0014互鎖，不可同時ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Z定位DO</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Y0014</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>前後定位縮回線圈</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>雙線圈閥B線圈</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>S305</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>正式採用</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>必須與Y0013互鎖，不可同時ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>廢止</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>X0044~X0047</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>舊增補Z定位DI</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>非BOM/PLC正式點位</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>不得引用</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>廢止</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>正式設計不得出現在02_XY點位表</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>廢止</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Y0025/Y0026</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>舊增補Z定位DO</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>錯誤4DI/2DO方案</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>不得引用</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>廢止</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>正式設計不得出現在02_XY點位表</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="72" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>對象</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>伸出線圈</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>縮回線圈</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>伸出完成</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>縮回完成</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>PLC寫法原則</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>異常判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>檢查站左右定位</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>Y0011</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>Y0012</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>X0016</t>
+        </is>
+      </c>
+      <c r="E2" s="16" t="inlineStr">
+        <is>
+          <t>X0017</t>
+        </is>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>伸出時：Y0011=ON且Y0012=OFF；縮回時：Y0011=OFF且Y0012=ON；Y0011/Y0012不可同時ON</t>
+        </is>
+      </c>
+      <c r="G2" s="16" t="inlineStr">
+        <is>
+          <t>同時ON為程式錯誤；Timeout未到位為停機異常</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>檢查站前後定位</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Y0013</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>Y0014</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>X0020</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>X0021</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>伸出時：Y0013=ON且Y0014=OFF；縮回時：Y0013=OFF且Y0014=ON；Y0013/Y0014不可同時ON</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>同時ON為程式錯誤；Timeout未到位為停機異常</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Fault/EMO/Air OFF</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>依停機策略</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>依停機策略</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>保留監看</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>保留監看</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>不得在異常中反覆切換線圈；先進Alarm等待人工排除</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>現場需確認雙線圈閥斷電是否保持最後位置</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>手動調機</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>HMI手動按鈕</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>HMI手動按鈕</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>對應DI</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>對應DI</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>工程模式才允許，且同組互鎖</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>未到位顯示Alarm/Warning</t>
         </is>
       </c>
     </row>

--- a/docs/PTC_Mask_Transfer_4Axis_Design_Draft.xlsx
+++ b/docs/PTC_Mask_Transfer_4Axis_Design_Draft.xlsx
@@ -36,6 +36,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_IO不可新增與待確認" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_IO補充_雙線圈版" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_雙線圈控制標準" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_20260826驗證封口" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -74,7 +75,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -121,8 +122,13 @@
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border/>
     <border>
       <left style="thin">
@@ -212,11 +218,39 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00666666"/>
+      </left>
+      <right style="thin">
+        <color rgb="00666666"/>
+      </right>
+      <top style="thin">
+        <color rgb="00666666"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00666666"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -265,6 +299,33 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -538,218 +599,243 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="51" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>00_設計標準總覽</t>
         </is>
       </c>
+      <c r="B1" s="26" t="n"/>
+      <c r="C1" s="26" t="n"/>
+      <c r="D1" s="26" t="n"/>
+      <c r="E1" s="26" t="n"/>
+      <c r="F1" s="26" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>類別</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="27" t="inlineStr">
         <is>
           <t>標準/分區</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="27" t="inlineStr">
         <is>
           <t>狀態</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="27" t="inlineStr">
         <is>
           <t>說明</t>
         </is>
       </c>
+      <c r="E2" s="28" t="n"/>
+      <c r="F2" s="28" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>文件目的</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>PLC/HMI 設計標準版 V2</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>PASS_TO_CODING</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>整合目前定案內容，移除舊矛盾與過程文字</t>
         </is>
       </c>
+      <c r="E3" s="28" t="n"/>
+      <c r="F3" s="28" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>適用範圍</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>X橫移、X升降、Z升降、Z旋轉、Barcode、HMI、安全/停止策略</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>設計文件</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>位址範圍限制 X/Y/M/D/T/S 0~6999</t>
         </is>
       </c>
+      <c r="E4" s="28" t="n"/>
+      <c r="F4" s="28" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>2軸流程</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>X橫移 + X升降</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>可進入 PLC Coding 與單機測試</t>
         </is>
       </c>
+      <c r="E5" s="28" t="n"/>
+      <c r="F5" s="28" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Z升降+Barcode</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>完整機構流程 + KEYENCE SR-2000W</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>完整機構流程 + KEYENCE Barcode Reader(依BOM實際採購型號)</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>可 Coding / 未實測</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>含定位氣缸、光罩在席、Z抬高、氣缸縮回、Barcode掃描位；通訊格式需實機確認</t>
         </is>
       </c>
+      <c r="E6" s="28" t="n"/>
+      <c r="F6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Z旋轉</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>僅手動/調機 0/90/180/270</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>自動禁用</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>Barcode 建議角度只供HMI顯示與人工調機參考</t>
         </is>
       </c>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>HMI</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>自動、手動調機、初始化、Barcode NG、I/O、Alarm、Recipe</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>可設計 / 待畫面實作</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>已補正向/反向啟動、Auto Stop、Auto Busy、初始化完成、Barcode生產前掃碼OK</t>
         </is>
       </c>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>整機 Release</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>現場驗收</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>SR-2000W通訊、Z高度、Tolerance、Safety OFF、真空/煞車/門鎖Bypass需實測</t>
-        </is>
-      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>Barcode Reader(依BOM實際採購型號)通訊、Z高度、Tolerance、Safety OFF、真空/煞車/門鎖Bypass需實測</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>成熟度</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>約 88%~90%</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>可進程式設計</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>比上一版更接近Coding版，但不是現場整機Release通過</t>
         </is>
       </c>
+      <c r="E10" s="28" t="n"/>
+      <c r="F10" s="28" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -766,7 +852,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -1202,7 +1288,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
@@ -2088,7 +2174,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -2719,7 +2805,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -3059,7 +3145,7 @@
       </c>
       <c r="G9" s="16" t="inlineStr">
         <is>
-          <t>Barcode型號依BOM/採購版統一；若目前BOM為SR-1000W，文件先以SR-1000W</t>
+          <t>Barcode型號依BOM/採購版統一；若目前BOM為Barcode Reader(依BOM實際採購型號)，文件先以Barcode Reader(依BOM實際採購型號)</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3383,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -3612,7 +3698,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -4180,570 +4266,750 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="64" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>代碼</t>
         </is>
       </c>
-      <c r="B1" s="20" t="n"/>
-      <c r="C1" s="20" t="n"/>
-      <c r="D1" s="20" t="n"/>
-      <c r="E1" s="20" t="n"/>
-      <c r="F1" s="21" t="n"/>
+      <c r="B1" s="26" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="C1" s="26" t="inlineStr">
+        <is>
+          <t>等級</t>
+        </is>
+      </c>
+      <c r="D1" s="26" t="inlineStr">
+        <is>
+          <t>觸發條件</t>
+        </is>
+      </c>
+      <c r="E1" s="26" t="inlineStr">
+        <is>
+          <t>PLC動作</t>
+        </is>
+      </c>
+      <c r="F1" s="26" t="inlineStr">
+        <is>
+          <t>排除/復歸</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>K101</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>安全繼電器NG</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="28" t="inlineStr">
         <is>
           <t>停機</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D2" s="28" t="inlineStr">
         <is>
           <t>X0000 OFF</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="28" t="inlineStr">
         <is>
           <t>停止自動；伺服禁止新命令；依安全策略切MC/煞車。</t>
         </is>
       </c>
-      <c r="F2" s="18" t="inlineStr">
+      <c r="F2" s="28" t="inlineStr">
         <is>
           <t>檢查EMO/門鎖，安全復歸M6042。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>K102</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>氣壓不足</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>停機</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>X0001 OFF</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>停止自動；保持或洩放真空依現場策略。</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="28" t="inlineStr">
         <is>
           <t>恢復氣壓後M6040復歸。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>K150</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>X橫移定位逾時/誤差過大</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>停機</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>Busy逾時或D423x&gt;D4100</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>轉S189。</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>排除卡滯/極限/伺服警報後初始化。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>K160</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>X升降定位逾時/誤差過大</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>停機</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>Busy逾時或D443x&gt;D4300</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>S200 SET M1228，主流程轉S189。</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>確認Z干涉、煞車、負載、位置參數後初始化。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>K171</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>X/Z交握逾時</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>停機</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>等待M6102或M6103逾時</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>RST M6101/M6102，轉S189。</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>確認Z流程、安全位、Barcode狀態。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>K180</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>氣缸到位異常</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>停機</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>夾爪或定位氣缸未到位</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>停止後續軸移動。</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>查電磁閥、磁簧、氣壓、機構。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>K181</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Barcode通訊逾時</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>停機/可重試</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>D6400讀取逾時</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>進Barcode NG/人工介入流程。</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>確認SR-2000W通訊、Trigger、網路。</t>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>確認Barcode Reader(依BOM實際採購型號)通訊、Trigger、網路。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>K182</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>Barcode比對NG</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>停機/人工判定</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>讀取字串與工單字串不一致</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>HMI彈窗，可重掃一次。</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>門鎖Bypass開門確認，關門安全恢復後判定。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>K200</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>真空建立失敗</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>停機</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>取片真空ON後X0027/X0030/X0031未成立</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>保持在安全位置，不上升或停止在真空確認位。</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>檢查吸盤、真空產生器、破真空閥、漏氣。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>K201</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>破真空失敗</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>停機/警告</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>破真空後真空OK未OFF</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>停止下一步放夾或要求人工確認。</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>檢查破真空電磁閥、管路阻塞。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>K210</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>靜電消除器檢查</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>警告</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>X0032 ON</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>不停機，HMI提示維護。</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>檢查清潔/放電針/氣源。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>K211</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>靜電消除器異常</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>停機</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>X0033 ON</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>停止自動流程，依風險決定是否保持真空。</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>排除設備異常後復歸。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>K220</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>排風壓差低</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>警告/停機待定</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>X0034 ON</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>可警告或禁止啟動，依業主規範。</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>檢查FFU/排風/濾網。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>K221</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>排風壓差高</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>警告/停機待定</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>X0035 ON</t>
         </is>
       </c>
-      <c r="E15" s="19" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>可警告或禁止啟動，依業主規範。</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>檢查濾網阻塞。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>K230</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>FFU異常</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="28" t="inlineStr">
         <is>
           <t>警告/停機待定</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>X0037 ON</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>依潔淨需求決定停機或禁止啟動。</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>查FFU電源、接觸器、濾網。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>K240</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>Z升降異常</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>停機</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>Z升降伺服/定位/Timeout</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="28" t="inlineStr">
         <is>
           <t>停止Z流程，主流程不允許X進入。</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>排除後初始化。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>K250</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Z旋轉手動異常</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>警告/停機</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>手動旋轉Alarm/Timeout</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>停止Z旋轉手動命令。</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>工程模式排除後復歸。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>K270</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>儲存盒關蓋等效條件未成立</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>警告/停機待定</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="inlineStr">
+        <is>
+          <t>Cycle Complete等待X0023 OFF逾時</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>禁止Y0020儲存盒破真空。</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
+        <is>
+          <t>確認儲存盒蓋/感測器語意，人工處理後復歸。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>K271</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>儲存盒破真空未完成</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>停機/警告</t>
+        </is>
+      </c>
+      <c r="D20" s="28" t="inlineStr">
+        <is>
+          <t>Y0020 ON後X0030未OFF且逾時</t>
+        </is>
+      </c>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>禁止Cycle End。</t>
+        </is>
+      </c>
+      <c r="F20" s="28" t="inlineStr">
+        <is>
+          <t>檢查儲存盒破真空閥/真空管路。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>K272</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>上機盒破真空未完成</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>停機/警告</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>Y0022 ON後X0031未OFF且逾時</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>禁止Cycle End。</t>
+        </is>
+      </c>
+      <c r="F21" s="28" t="inlineStr">
+        <is>
+          <t>檢查上機盒破真空閥/真空管路。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>K273</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t>兩盒未取出</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>警告</t>
+        </is>
+      </c>
+      <c r="D22" s="28" t="inlineStr">
+        <is>
+          <t>等待X0022 OFF AND X0024 OFF逾時</t>
+        </is>
+      </c>
+      <c r="E22" s="28" t="inlineStr">
+        <is>
+          <t>保持完成提示，不進下一循環。</t>
+        </is>
+      </c>
+      <c r="F22" s="28" t="inlineStr">
+        <is>
+          <t>操作員取出兩盒後自動解除或按復歸。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>K274</t>
+        </is>
+      </c>
+      <c r="B23" s="28" t="inlineStr">
+        <is>
+          <t>上機盒關蓋等效條件未成立</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>警告/停機待定</t>
+        </is>
+      </c>
+      <c r="D23" s="28" t="inlineStr">
+        <is>
+          <t>Cycle Complete等待X0025 OFF逾時</t>
+        </is>
+      </c>
+      <c r="E23" s="28" t="inlineStr">
+        <is>
+          <t>禁止Y0022上機盒破真空。</t>
+        </is>
+      </c>
+      <c r="F23" s="28" t="inlineStr">
+        <is>
+          <t>確認上機盒蓋/感測器語意，人工處理後復歸。</t>
         </is>
       </c>
     </row>
@@ -4761,202 +5027,256 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="76" customWidth="1" min="3" max="3"/>
-    <col width="76" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
+    <col width="51" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="20" t="n"/>
-      <c r="C1" s="20" t="n"/>
-      <c r="D1" s="20" t="n"/>
-      <c r="E1" s="20" t="n"/>
-      <c r="F1" s="21" t="n"/>
+      <c r="B1" s="26" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="C1" s="26" t="inlineStr">
+        <is>
+          <t>目前設計狀態</t>
+        </is>
+      </c>
+      <c r="D1" s="26" t="inlineStr">
+        <is>
+          <t>Coding/驗收注意事項</t>
+        </is>
+      </c>
+      <c r="E1" s="26" t="inlineStr"/>
+      <c r="F1" s="26" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>PLC/HMI設計文件</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>PASS_TO_CODING</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>已整合審查P0/P1主要問題，可作Coding依據。</t>
-        </is>
-      </c>
-      <c r="D2" s="16" t="inlineStr">
-        <is>
-          <t>依本表Coding，不再沿用舊衝突點位。</t>
-        </is>
-      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>已整合20260826來源設計最終封口建議，可作Coding依據。</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>依正式X/Y、M/D/T/S表Coding，不沿用舊衝突點位。</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr"/>
+      <c r="F2" s="28" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>正式X/Y點位</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>02_XY點位表維持BOM/PLC已確認點位，未新增X0044~X0047/Y0025/Y0026。</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>新增需求只能先列待確認，不可直接佔用正式X/Y。</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr"/>
+      <c r="F3" s="28" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>2軸流程</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>X橫移/X升降正反向、初始化、異常復歸已定義。</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>單機測試D441x/D443x。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>X橫移/X升降正反向、初始化、真空確認、異常復歸已定義。</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>單機測試D441x/D443x、D4100/D4300。</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr"/>
+      <c r="F4" s="28" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Z升降+Barcode</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>可Coding</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>流程完整但SR-2000W通訊未實測。</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>確認字串長度、Byte order、Timeout、重掃流程。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>可Coding/HOLD</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>S300含檢查站定位、Z平台抬高、定位縮回、Barcode位、比對、回安全位。</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Barcode Reader實際型號依BOM；通訊格式、字串長度、Byte order、Timeout需實測。</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr"/>
+      <c r="F5" s="28" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Z旋轉</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>只限手動/調機；自動流程禁止使用。</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>PASS_TO_MANUAL</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>S400只限手動/調機；自動流程禁止使用D6412旋轉。</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>測0/90/180/270與回原點後移0位。</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>HMI完整操作</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>可Coding</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>自動、手動、Alarm、Barcode、Reset、I/O監看已列。</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>實機驗證按鈕安全互鎖。</t>
-        </is>
-      </c>
+      <c r="E6" s="28" t="inlineStr"/>
+      <c r="F6" s="28" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Cycle Complete</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>已拆成儲存盒關蓋等效→儲存盒破真空→上機盒關蓋等效→上機盒破真空→兩盒取出。</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>需現場確認X0023/X0025 OFF是否等同關蓋。</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr"/>
+      <c r="F7" s="28" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Ionizer</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>Enable條件已修為停止輸出OFF、異常OFF、檢查訊號正常。</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>需確認DTY-ELK01 X0032檢查訊號正常/異常邏輯。</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr"/>
+      <c r="F8" s="28" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Safety Stop策略</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>現場待定</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>D4100/D4300/D4504/D4704需依pulse/mm與機構精度實測。</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>填入預設值、上下限、權限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>Safety Stop策略</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>現場待定</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>Safety OFF、Air OFF、真空保持/破真空、煞車落下策略需業主/機構確認。</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>FAT前封口。</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr"/>
+      <c r="F9" s="28" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>整機Release</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>尚未實機測試，不可判定量產驗收通過。</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>文件可進程式設計與單機測試，但尚未實機測試，不可判定量產驗收通過。</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>完成FAT/SAT後再Release。</t>
         </is>
       </c>
+      <c r="E10" s="28" t="inlineStr"/>
+      <c r="F10" s="28" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4973,7 +5293,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="112" customWidth="1" min="2" max="2"/>
@@ -5080,7 +5400,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>X0000、M6020、M4330、M6103、M6104、D6412、SR-2000W、S400手動限定</t>
+          <t>X0000、M6020、M4330、M6103、M6104、D6412、Barcode Reader(依BOM實際採購型號)、S400手動限定</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -5104,7 +5424,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -5218,7 +5538,7 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>SR-2000W通訊格式與Timeout需實測。</t>
+          <t>Barcode Reader(依BOM實際採購型號)通訊格式與Timeout需實測。</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5604,7 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>FAT/SAT前需完成SR-2000W、Z高度、Tolerance、Safety OFF、Air OFF、真空/煞車策略實測。</t>
+          <t>FAT/SAT前需完成Barcode Reader(依BOM實際採購型號)、Z高度、Tolerance、Safety OFF、Air OFF、真空/煞車策略實測。</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5620,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -6060,7 +6380,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -6561,8 +6881,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -7250,6 +7570,176 @@
       <c r="G18" s="16" t="n"/>
       <c r="H18" s="16" t="n"/>
     </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Cycle Complete盒蓋未確認</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>警告/保持</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>M6600 ON後X0023或X0025仍在開蓋定位</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>禁止Y0020/Y0022破真空，HMI提示關蓋</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>K270</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>不新增DI；X0023/X0025語意需現場確認</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="n"/>
+      <c r="H19" s="22" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>儲存盒破真空未完成</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>警告/保持</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>Y0020 ON後X0030仍ON或Timeout</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>保持Cycle Complete畫面，提示檢查儲存盒真空</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>K271</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>依真空表/時間決定</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="n"/>
+      <c r="H20" s="22" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>上機盒破真空未完成</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>警告/保持</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>Y0022 ON後X0031仍ON或Timeout</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>保持Cycle Complete畫面，提示檢查上機盒真空</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>K272</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>依真空表/時間決定</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="n"/>
+      <c r="H21" s="22" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>兩盒未取出</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>警告</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>等待X0022 OFF AND X0024 OFF逾時</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>流程不進下一Cycle，HMI提示取出盒</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>K273</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>非立即停機，但禁止下一輪</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="n"/>
+      <c r="H22" s="22" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>靜電消除器Ready不足</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>警告/可停機</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>Ionizer Enable ON但X0033異常ON或X0032檢查不正常</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>依工藝要求警告或停機；HMI顯示Ionizer NG</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>K210/K211</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>Y0023為停止輸出，Enable時應OFF</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7262,7 +7752,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -7565,7 +8055,7 @@
       </c>
       <c r="G8" s="19" t="inlineStr">
         <is>
-          <t>依SR-2000W實測通訊時間。</t>
+          <t>依Barcode Reader(依BOM實際採購型號)實測通訊時間。</t>
         </is>
       </c>
     </row>
@@ -7581,7 +8071,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -8040,7 +8530,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="54" customWidth="1" min="2" max="2"/>
@@ -8288,7 +8778,7 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>SR-2000W、Z高度、Tolerance、Safety Stop需實測</t>
+          <t>Barcode Reader(依BOM實際採購型號)、Z高度、Tolerance、Safety Stop需實測</t>
         </is>
       </c>
     </row>
@@ -8303,604 +8793,432 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="72" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>位址</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>類別</t>
+        </is>
+      </c>
+      <c r="B1" s="23" t="inlineStr">
+        <is>
+          <t>點位</t>
+        </is>
+      </c>
+      <c r="C1" s="23" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>類型</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>用途</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>判斷條件</t>
-        </is>
-      </c>
-      <c r="F1" s="14" t="inlineStr">
-        <is>
-          <t>來源</t>
-        </is>
-      </c>
-      <c r="G1" s="14" t="inlineStr">
-        <is>
-          <t>風險</t>
-        </is>
-      </c>
-      <c r="H1" s="14" t="inlineStr">
-        <is>
-          <t>備註</t>
+      <c r="D1" s="23" t="inlineStr">
+        <is>
+          <t>正式處置</t>
+        </is>
+      </c>
+      <c r="E1" s="23" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+      <c r="F1" s="23" t="inlineStr">
+        <is>
+          <t>是否可用</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>X0044</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>Z檢查站_左右定位伸出完成</t>
-        </is>
-      </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="D2" s="16" t="inlineStr">
-        <is>
-          <t>左右2支定位氣缸伸出回授串/並接後進PLC；兩支皆伸出才ON。</t>
-        </is>
-      </c>
-      <c r="E2" s="16" t="inlineStr">
-        <is>
-          <t>ON=伸出完成</t>
-        </is>
-      </c>
-      <c r="F2" s="16" t="inlineStr">
-        <is>
-          <t>4軸完整需求建議表</t>
-        </is>
-      </c>
-      <c r="G2" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H2" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Z定位正式DI</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>X0016</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>檢查站氣缸左右定位_開</t>
+        </is>
+      </c>
+      <c r="D2" s="22" t="inlineStr">
+        <is>
+          <t>使用正式點位</t>
+        </is>
+      </c>
+      <c r="E2" s="22" t="inlineStr">
+        <is>
+          <t>左右2支伸出磁簧串聯後ON。</t>
+        </is>
+      </c>
+      <c r="F2" s="22" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>X0045</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>Z檢查站_左右定位縮回完成</t>
-        </is>
-      </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>左右2支定位氣缸縮回完成。</t>
-        </is>
-      </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>ON=縮回完成</t>
-        </is>
-      </c>
-      <c r="F3" s="16" t="inlineStr">
-        <is>
-          <t>4軸完整需求建議表</t>
-        </is>
-      </c>
-      <c r="G3" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H3" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>Z定位正式DI</t>
+        </is>
+      </c>
+      <c r="B3" s="22" t="inlineStr">
+        <is>
+          <t>X0017</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t>檢查站氣缸左右定位_關</t>
+        </is>
+      </c>
+      <c r="D3" s="22" t="inlineStr">
+        <is>
+          <t>使用正式點位</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t>左右2支縮回磁簧串聯後ON。</t>
+        </is>
+      </c>
+      <c r="F3" s="22" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>X0046</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Z檢查站_前後定位伸出完成</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>前後2支定位氣缸伸出完成。</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>ON=伸出完成</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>4軸完整需求建議表</t>
-        </is>
-      </c>
-      <c r="G4" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H4" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>Z定位正式DI</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>X0020</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>檢查站氣缸前後定位_開</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>使用正式點位</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>前後2支伸出磁簧串聯後ON。</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>X0047</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>Z檢查站_前後定位縮回完成</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>前後2支定位氣缸縮回完成。</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>ON=縮回完成</t>
-        </is>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>4軸完整需求建議表</t>
-        </is>
-      </c>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Z定位正式DI</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>X0021</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>檢查站氣缸前後定位_關</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>使用正式點位</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>前後2支縮回磁簧串聯後ON。</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>X0050</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>安全門_關閉回授</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>PLC監看用，安全功能仍走安全繼電器。</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>ON=門關閉</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>4軸完整需求建議表</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Z定位正式DO</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Y0011</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>檢查站左右電磁閥_開</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>使用正式點位</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>雙線圈A，與Y0012不可同時ON。</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>X0051</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>安全門_鎖定回授</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>PLC監看門鎖狀態。</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>ON=門鎖定</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>4軸完整需求建議表</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Z定位正式DO</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Y0012</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>檢查站左右電磁閥_關</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>使用正式點位</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>雙線圈B，與Y0011不可同時ON。</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>X0052</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>儲存盒盒蓋關閉</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>完成流程後才允許儲存盒破真空/取盒。</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>ON=盒蓋關閉</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>4軸完整需求建議表</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Z定位正式DO</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>Y0013</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>檢查站前後電磁閥_開</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>使用正式點位</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>雙線圈A，與Y0014不可同時ON。</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>X0053</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>上機盒盒蓋關閉</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>完成流程後才允許上機盒破真空/取盒。</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>ON=盒蓋關閉</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>4軸完整需求建議表</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>Z定位正式DO</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Y0014</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>檢查站前後電磁閥_關</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>使用正式點位</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>雙線圈B，與Y0013不可同時ON。</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>Y0025</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>Z檢查站_左右定位電磁閥</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>控制左右2支定位氣缸，同組動作。</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>ON=定位伸出</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>4軸完整需求建議表</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>盒蓋條件</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>X0023</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>儲存盒開蓋定位</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>不新增DI，作Cycle Complete暫定條件</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>OFF暫定代表不在開蓋位；需現場確認是否等同關蓋。</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>Y0026</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>Z檢查站_前後定位電磁閥</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>控制前後2支定位氣缸，同組動作。</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>ON=定位伸出</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>4軸完整需求建議表</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>盒蓋條件</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>X0025</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>上機盒開蓋定位</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>不新增DI，作Cycle Complete暫定條件</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>OFF暫定代表不在開蓋位；需現場確認是否等同關蓋。</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Y0027</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>安全門解鎖請求</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>PLC只送請求，不旁路安全。</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>ON=請求解鎖</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>4軸完整需求建議表</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>廢止</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>X0044~X0047</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>舊Z定位DI新增方案</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>不得使用</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>正式X/Y表不得新增；HMI/Sequence不得引用。</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Y0030</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>儲存盒破真空</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>盒蓋關閉後才允許。</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>ON=破真空</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>4軸完整需求建議表</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Y0031</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>上機盒破真空</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>盒蓋關閉後才允許。</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>ON=破真空</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>4軸完整需求建議表</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>待畫圖</t>
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>廢止</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Y0025/Y0026</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>舊Z定位DO新增方案</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>不得使用</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>正式X/Y表不得新增；HMI/Sequence不得引用。</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -8915,612 +9233,787 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>流程段</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>主要動作</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>使用軸/輸出</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
+        <is>
+          <t>動作說明</t>
+        </is>
+      </c>
+      <c r="D1" s="26" t="inlineStr">
+        <is>
+          <t>使用M/D/Y/X</t>
+        </is>
+      </c>
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>完成條件</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
-        <is>
-          <t>異常處理</t>
-        </is>
-      </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
+        <is>
+          <t>異常/Timeout</t>
+        </is>
+      </c>
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="n">
+      <c r="A2" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>Auto Ready</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="28" t="inlineStr">
         <is>
           <t>確認Safety/Air/FFU/初始化/Barcode條件</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="28" t="inlineStr">
         <is>
           <t>X0000/X0001/X0036/X0037/M1125/M1225/M1425</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="28" t="inlineStr">
         <is>
           <t>Ready成立</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="28" t="inlineStr">
         <is>
           <t>不成立禁止啟動</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="G2" s="28" t="inlineStr">
         <is>
           <t>Barcode Enable ON時需Storage Barcode Valid</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>X取來源盒</t>
-        </is>
-      </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>X橫移到來源位，X升降到取片位，夾爪關，真空ON</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>X取片前置</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>X橫移到來源盒；X升降到取片位；夾爪關；真空ON</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>Axis1/Axis2/Y0010/Y0015</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>X0015+X0027</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="28" t="inlineStr">
         <is>
           <t>真空NG-&gt;S189/S299</t>
         </is>
       </c>
-      <c r="G3" s="16" t="inlineStr">
-        <is>
-          <t>正向來源=儲存盒；反向來源=上機盒</t>
+      <c r="G3" s="28" t="inlineStr">
+        <is>
+          <t>來源依方向=儲存盒或上機盒</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>X真空確認上升</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>上升約10mm到真空確認位，再確認真空OK</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>X取片真空確認</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>X升降上升10mm至真空確認位，確認吸住</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>Axis2/M4330</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>X0027保持ON</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>X0027持續ON</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>真空掉落停機</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
-        <is>
-          <t>確認後升到上位</t>
+      <c r="G4" s="28" t="inlineStr">
+        <is>
+          <t>若三位置高度不同，D43xx需現場Teach</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>X移到檢查位</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>X搬到檢查位</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>X升降上位後，X橫移到檢查位</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>Axis1</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>M4151 ON</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>Axis Alarm停機</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>到位後才下降</t>
+      <c r="G5" s="28" t="inlineStr">
+        <is>
+          <t>光罩不得與Z干涉</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>X放到檢查站</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>X升降到檢查放位，破真空，夾爪開</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>X放到檢查位</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>X升降到檢查位放片高度；破真空；夾爪開</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>Axis2/Y0016/Y0007</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>X0014+X0026</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>光罩未在席-&gt;Alarm</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>放完X回上位再離開干涉區</t>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>光罩在席未成立-&gt;Alarm</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>放片完成後X升降回上位</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>X離開檢查位</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>X升降回上位，X橫移離開檢查區</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>X升降回上位後，X橫移離開檢查位到安全位置</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>Axis1/Axis2</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>X已Clear</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>X區域Clear</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>未Clear禁止Z</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>避免Z軸動作干涉</t>
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>避免Z升降/旋轉干涉</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Z左右定位伸出</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>左右雙線圈閥伸出</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>檢查站左右定位雙線圈伸出</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>Y0011 ON/Y0012 OFF</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>X0016 ON</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>K310</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>2支磁簧串聯</t>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>雙線圈互斥</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n">
+      <c r="A9" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>Z前後定位伸出</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>前後雙線圈閥伸出</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>檢查站前後定位雙線圈伸出</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>Y0013 ON/Y0014 OFF</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>X0020 ON</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>K311</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>2支磁簧串聯</t>
+      <c r="G9" s="28" t="inlineStr">
+        <is>
+          <t>雙線圈互斥</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n">
+      <c r="A10" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>Z升平台位</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>確認X0026後Z升到平台位</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Z平台抬高</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>確認X0026後，Z升到平台位抬高光罩</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>Axis3/M4521/D4514</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>M4551 ON</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>K320</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>啟動前需X0016+X0020+X0026</t>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>前置確認X0016+X0020+X0026</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n">
+      <c r="A11" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>Z定位縮回</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>左右/前後雙線圈閥縮回</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>左右/前後定位雙線圈縮回</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>Y0012 ON/Y0014 ON</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>X0017 AND X0021</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>K321</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="28" t="inlineStr">
         <is>
           <t>縮回後才可去Barcode</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n">
+      <c r="A12" s="28" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Z到Barcode位</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>Z升降到掃碼高度</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>Axis3/M4522/D4510</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>M4552 ON</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>K322</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t>高度現場Teach</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n">
+      <c r="A13" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>Barcode/Visual</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>掃碼、比對、目視檢查選配</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>M630x/M650x</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>OK/BYPASS</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>NG-&gt;回來源盒</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G13" s="28" t="inlineStr">
         <is>
           <t>Axis4不參與Auto</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n">
+      <c r="A14" s="28" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>Z回Home</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>Z升降回Home</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Z回安全位</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>Z升降回Home/安全位</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>Axis3/M4520/D4512</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>M4550 ON</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>K350</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>固定Home Complete</t>
+      <c r="G14" s="28" t="inlineStr">
+        <is>
+          <t>SET M6103通知X</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n">
+      <c r="A15" s="28" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>X回檢查位取片</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>X回檢查位，下降取片，真空確認，上升</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>X取檢查位光罩</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>X回檢查位，下降取片，夾爪關，真空ON</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>Axis1/Axis2/Y0010/Y0015</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>X0027 ON</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>真空NG停機</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>準備送目的盒</t>
+      <c r="G15" s="28" t="inlineStr">
+        <is>
+          <t>取回已檢查光罩</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="28" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>X送目的盒</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>PASS送目的盒；NG回來源盒</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>X放目的盒</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>PASS放目的盒；NG回來源盒</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>Axis1/Axis2/Y0016/Y0007</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>放片完成</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>未到位/真空異常停機</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>正反向依D6100/M6002/M6003</t>
+      <c r="F16" s="28" t="inlineStr">
+        <is>
+          <t>下降位置或真空異常停機</t>
+        </is>
+      </c>
+      <c r="G16" s="28" t="inlineStr">
+        <is>
+          <t>方向由D6100/M6002/M6003決定</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="28" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>Cycle Complete</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>允許開門/移除盒，等待兩盒移除</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>M6600/Y0020/Y0022/X0022/X0024</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>Cycle Complete-等待關儲存盒蓋</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>流程完成後，要求關閉儲存盒蓋；不新增DI。</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="inlineStr">
+        <is>
+          <t>M6600 ON；監看X0023</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>X0023 OFF</t>
+        </is>
+      </c>
+      <c r="F17" s="28" t="inlineStr">
+        <is>
+          <t>逾時警告K270</t>
+        </is>
+      </c>
+      <c r="G17" s="28" t="inlineStr">
+        <is>
+          <t>X0023為儲存盒開蓋定位，OFF暫定視為不在開蓋位；需現場確認是否等同關蓋。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>Cycle Complete-儲存盒破真空</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="inlineStr">
+        <is>
+          <t>儲存盒關蓋等效條件成立後才允許儲存盒破真空。</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="inlineStr">
+        <is>
+          <t>Y0020 ON</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>X0030 OFF 或到破真空時間</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
+        <is>
+          <t>真空未釋放K271</t>
+        </is>
+      </c>
+      <c r="G18" s="28" t="inlineStr">
+        <is>
+          <t>不得在儲存盒蓋未關時破真空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>Cycle Complete-等待關上機盒蓋</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>要求關閉上機盒蓋；不新增DI。</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="inlineStr">
+        <is>
+          <t>監看X0025</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>X0025 OFF</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
+        <is>
+          <t>逾時警告K274</t>
+        </is>
+      </c>
+      <c r="G19" s="28" t="inlineStr">
+        <is>
+          <t>X0025為上機盒開蓋定位，OFF暫定視為不在開蓋位；需現場確認是否等同關蓋。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>Cycle Complete-上機盒破真空</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>上機盒關蓋等效條件成立後才允許上機盒破真空。</t>
+        </is>
+      </c>
+      <c r="D20" s="28" t="inlineStr">
+        <is>
+          <t>Y0022 ON</t>
+        </is>
+      </c>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>X0031 OFF 或到破真空時間</t>
+        </is>
+      </c>
+      <c r="F20" s="28" t="inlineStr">
+        <is>
+          <t>真空未釋放K272</t>
+        </is>
+      </c>
+      <c r="G20" s="28" t="inlineStr">
+        <is>
+          <t>不得在上機盒蓋未關時破真空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>Cycle Complete-取出兩盒</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>提示操作員取出儲存盒與上機盒。</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>HMI Popup；Y0020/Y0022依策略OFF</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>X0022 OFF AND X0024 OFF</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>逾時警告</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>不新增門鎖X/Y，門鎖若需PLC監看另走擴充點位</t>
+      <c r="F21" s="28" t="inlineStr">
+        <is>
+          <t>逾時警告K273</t>
+        </is>
+      </c>
+      <c r="G21" s="28" t="inlineStr">
+        <is>
+          <t>此步才算Cycle End。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t>Cycle End</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>清除Auto Busy與流程旗標，寫入History。</t>
+        </is>
+      </c>
+      <c r="D22" s="28" t="inlineStr">
+        <is>
+          <t>RST M6600；SET M6604</t>
+        </is>
+      </c>
+      <c r="E22" s="28" t="inlineStr">
+        <is>
+          <t>可回Auto Ready</t>
+        </is>
+      </c>
+      <c r="F22" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="28" t="inlineStr">
+        <is>
+          <t>History記錄Barcode/Visual/方向/結果。</t>
         </is>
       </c>
     </row>
@@ -9536,271 +10029,271 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="51" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="51" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>必要性</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>HMI設定</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>Auto Ready條件</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>OFF時流程行為</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>異常/顯示</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>Safety Relay</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="28" t="inlineStr">
         <is>
           <t>不可Bypass</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="28" t="inlineStr">
         <is>
           <t>X0000 ON</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="28" t="inlineStr">
         <is>
           <t>OFF禁止Auto且安全硬體處理</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="28" t="inlineStr">
         <is>
           <t>K101</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="G2" s="28" t="inlineStr">
         <is>
           <t>不能由PLC旁路。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>Air Pressure</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>不可Bypass</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>X0001 ON</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>OFF禁止Auto</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="28" t="inlineStr">
         <is>
           <t>K102</t>
         </is>
       </c>
-      <c r="G3" s="16" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t>掉片策略見Fault Matrix。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>FFU</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>必須/依業主</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>不可Bypass或工程限定</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>Run ON + Alarm OFF</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>不成立禁止Auto Start或停在安全點</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>K230</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="28" t="inlineStr">
         <is>
           <t>依潔淨需求決定停機等級。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Ionizer</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>可選</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>Ionizer Enable</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>ON時需無Alarm</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>OFF只Bypass靜電消除判斷</t>
-        </is>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Enable時：Y0023靜電消除器停止=OFF，X0033異常=OFF，X0032檢查訊號依DTY-ELK01手冊/實機定義判定正常。</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>OFF只Bypass靜電消除判斷，HMI需顯示Bypass。</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>K210/K211</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>HMI需顯示Bypass。</t>
+      <c r="G5" s="28" t="inlineStr">
+        <is>
+          <t>若無Run回授，Ready不可只看Alarm OFF；需以停止命令OFF+Alarm OFF+檢查訊號正常定義。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Barcode Compare</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>可選但建議必用</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>Barcode Enable</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>ON時M6301 Storage Barcode Valid必須ON</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>OFF記錄BYPASS，不做比對</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>K181/K182</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>若業主要求條碼追溯，建議不可Bypass。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Visual Inspection</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>可選</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>Visual Enable</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>ON時Barcode OK後要求人工判定</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>OFF記錄BYPASS</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>K260</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="28" t="inlineStr">
         <is>
           <t>人工確認流程。</t>
         </is>
@@ -9818,7 +10311,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -9905,7 +10398,7 @@
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>PLC觸發SR-2000W，結果寫D6350起始區。</t>
+          <t>PLC觸發Barcode Reader(依BOM實際採購型號)，結果寫D6350起始區。</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -10095,456 +10588,492 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="66" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
+    <col width="51" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="51" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>畫面</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>要求</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>點位/資料</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>權限</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>Auto首頁</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>Machine Ready</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="28" t="inlineStr">
         <is>
           <t>顯示Safety/Air/FFU/Init/Barcode Valid/Visual Enable/Alarm成立狀態。</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="28" t="inlineStr">
         <is>
           <t>X0000/X0001/M6301/M6500/D6004</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="28" t="inlineStr">
         <is>
           <t>Operator</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr"/>
+      <c r="F2" s="28" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>Auto首頁</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Forward/Reverse Start</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>正向/反向啟動，Busy時禁止反向。</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>M6002/M6003</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>Operator</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr"/>
+      <c r="F3" s="29" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Auto首頁</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>流程完成Popup</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>顯示可開門、關盒蓋、取出兩盒。</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>M6600/D6600</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>Operator</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr"/>
+      <c r="F4" s="28" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>功能設定</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Ionizer Enable</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>ON/OFF並顯示Bypass。</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>Ionizer Enable/M650x</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>Engineer</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr"/>
+      <c r="F5" s="28" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>功能設定</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Barcode Compare Enable</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>ON時Storage Barcode Valid必要。</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>M6300/M6301</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>Engineer</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr"/>
+      <c r="F6" s="28" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>功能設定</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Visual Inspection Enable</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>ON時需人工OK/NG。</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>M6500</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>Engineer</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr"/>
+      <c r="F7" s="29" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Barcode畫面</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Storage Barcode</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>輸入/顯示/Valid。</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>D6300~D6349/M6301</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>Operator/Engineer</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr"/>
+      <c r="F8" s="28" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>Barcode畫面</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Mask Barcode/Compare</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>顯示讀取值、OK/NG/BYPASS。</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>D6350~D6399/M6304/M6305/M6306</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>Operator</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr"/>
+      <c r="F9" s="30" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>Barcode History</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>1000筆歷史</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>最新一筆在第1列，可依方向/結果篩選。</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>HMI Ring Buffer/Data Logging</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>Operator</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>建議HMI處理。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Visual Popup</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>人工目視確認</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>Visual Enable ON且Barcode OK後彈窗，流程Hold。</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>M6501/M6502/M6503/D6500</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>Operator</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>NG需二次確認。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>工程調機</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>4軸JOG</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>Axis1~Axis4 JOG，Axis4只允許工程/手動。</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>M4131/M4132/M4341/M4340/M4531/M4532/M4731/M4732</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>Engineer</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>需M6200/M6201。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>工程調機</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>4軸Teach</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>Current/Target/Teach/Save/Confirm。</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>D4100~D4899</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>Engineer</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>Auto Busy禁止。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>工程調機</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Z定位氣缸診斷</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>顯示LR/FB伸出縮回與Valve狀態。</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>X0044~X0047/Y0025/Y0026</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>顯示檢查站左右/前後定位雙線圈伸出、縮回與回授狀態。</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>X0016/X0017/X0020/X0021 + Y0011/Y0012/Y0013/Y0014</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>Engineer</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr"/>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>Deprecated Device不得引用；HMI只顯示正式4DI+4DO。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>異常畫面</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>Alarm Detail</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>顯示Alarm code、Step、Axis、Material State、Barcode/Visual result。</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>D6004/D6006/D6008/D6010/D6402/D6500</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>Operator</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr"/>
+      <c r="F15" s="28" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>Cycle Complete Popup</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>流程完成取盒導引</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>依序顯示：流程完成→請關儲存盒蓋→儲存盒破真空完成→請關上機盒蓋→上機盒破真空完成→請取出兩盒。</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
+        <is>
+          <t>M6600/M6601/M6602/M6603/M6604 + X0022/X0023/X0024/X0025 + Y0020/Y0022</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="F16" s="28" t="inlineStr">
+        <is>
+          <t>盒蓋關閉不新增DI；使用X0023/X0025開蓋定位OFF作暫定等效條件，現場需確認感測器語意。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10558,7 +11087,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F62"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -12567,8 +13096,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -12841,7 +13370,7 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>若BOM為SR-1000W，文件以SR-1000W；若採購改SR-2000W須同步BOM</t>
+          <t>若BOM為Barcode Reader(依BOM實際採購型號)，文件以Barcode Reader(依BOM實際採購型號)；若採購改Barcode Reader(依BOM實際採購型號)須同步BOM</t>
         </is>
       </c>
       <c r="F9" s="19" t="inlineStr">
@@ -12967,6 +13496,36 @@
       <c r="F13" s="19" t="inlineStr">
         <is>
           <t>16_驗收_Release_Gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Barcode型號一致性</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>完成/待採購封口</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>全設計文字改為Barcode Reader(依BOM實際採購型號)；採購確定Barcode Reader(依BOM實際採購型號)或Barcode Reader(依BOM實際採購型號)後再全檔替換成唯一型號。</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>BOM/採購單</t>
         </is>
       </c>
     </row>
@@ -12982,7 +13541,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -13165,7 +13724,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -13595,7 +14154,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -13796,6 +14355,312 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="26" t="inlineStr">
+        <is>
+          <t>驗證結果</t>
+        </is>
+      </c>
+      <c r="C1" s="26" t="inlineStr">
+        <is>
+          <t>處理方式</t>
+        </is>
+      </c>
+      <c r="D1" s="26" t="inlineStr">
+        <is>
+          <t>設計位置</t>
+        </is>
+      </c>
+      <c r="E1" s="26" t="inlineStr">
+        <is>
+          <t>剩餘現場確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>正式X/Y不可新增</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>02_XY點位表維持已確認點位；X0044~X0047/Y0025/Y0026只允許出現在Deprecated/不可新增說明。</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>02_XY點位表、01_IO新增與配置、26_IO不可新增與待確認</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>HMI Z定位診斷</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>改用X0016/X0017/X0020/X0021 + Y0011/Y0012/Y0013/Y0014。</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>24_HMI_4軸畫面</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Z定位雙線圈</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Y0011/Y0012、Y0013/Y0014互斥；伸出/縮回都有回授。</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>12_流程_Z升降_Barcode_S300、21_4軸Auto完整流程、27_雙線圈控制標準</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Barcode型號一致性</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>全檔統一寫Barcode Reader(依BOM實際採購型號)，不硬寫Barcode Reader(依BOM實際採購型號)或Barcode Reader(依BOM實際採購型號)。</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>08_D資料參數、12_S300、14_HMI、16_Release、23_History</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>採購/BOM封口後全檔替換唯一型號。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Cycle Complete-儲存盒</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>先確認X0023 OFF作為儲存盒關蓋等效條件，再允許Y0020破真空。</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>21_4軸Auto完整流程、15_異常警報標準、24_HMI_4軸畫面</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>確認X0023 OFF是否等同關蓋。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Cycle Complete-上機盒</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>先確認X0025 OFF作為上機盒關蓋等效條件，再允許Y0022破真空。</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>21_4軸Auto完整流程、15_異常警報標準、24_HMI_4軸畫面</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>確認X0025 OFF是否等同關蓋。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Cycle Complete-取出兩盒</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>PASS/HOLD</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>破真空完成後等待X0022 OFF AND X0024 OFF才Cycle End。</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>21_4軸Auto完整流程</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>確認在席Sensor OFF反應時間。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>門鎖策略</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>PLC/HMI只做提示與工程Bypass流程，不新增門鎖I/O。</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>20_HMI權限與互鎖、21_4軸Auto完整流程</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>安全迴路/門鎖硬體圖需現場封口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Ionizer Enable</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>Enable時需Y0023停止輸出OFF、X0033異常OFF、X0032檢查訊號正常。</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>22_功能Enable矩陣、15_異常警報標準</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>確認DTY-ELK01 X0032檢查訊號正常邏輯。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>最終判定</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>PASS_TO_CODING / RELEASE_HOLD</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>可進PLC/HMI程式設計與單機測試；整機Release仍需實機驗證。</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>16_驗收_Release_Gate</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>Barcode、Tolerance、Z高度、Safety Stop、真空/煞車策略。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -13803,7 +14668,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F86"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -16384,7 +17249,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -17077,7 +17942,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -18266,7 +19131,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -19007,7 +19872,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -19756,7 +20621,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F84"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -20754,7 +21619,7 @@
       </c>
       <c r="F34" s="16" t="inlineStr">
         <is>
-          <t>到SR-2000W掃描高度。</t>
+          <t>到Barcode Reader(依BOM實際採購型號)掃描高度。</t>
         </is>
       </c>
     </row>
@@ -20850,7 +21715,7 @@
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
-          <t>SR-2000W比對標準資料起始。</t>
+          <t>Barcode Reader(依BOM實際採購型號)比對標準資料起始。</t>
         </is>
       </c>
     </row>
@@ -20882,7 +21747,7 @@
       </c>
       <c r="F38" s="16" t="inlineStr">
         <is>
-          <t>SR-2000W讀取結果起始。</t>
+          <t>Barcode Reader(依BOM實際採購型號)讀取結果起始。</t>
         </is>
       </c>
     </row>
